--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
     <sheet name="红装" sheetId="2" r:id="rId2"/>
+    <sheet name="生肖" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -93,8 +94,41 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+ID* 10 + level
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="61">
   <si>
     <t>_ID</t>
   </si>
@@ -117,16 +151,7 @@
     <t>PartList</t>
   </si>
   <si>
-    <t>StartLevel</t>
-  </si>
-  <si>
-    <t>EndLevel</t>
-  </si>
-  <si>
-    <t>StartQuality</t>
-  </si>
-  <si>
-    <t>EndQuality</t>
+    <t>Cycle</t>
   </si>
   <si>
     <t>MaxCount</t>
@@ -211,6 +236,81 @@
   </si>
   <si>
     <t>2,4,5,9,10</t>
+  </si>
+  <si>
+    <t>21,23</t>
+  </si>
+  <si>
+    <t>21,22,23,24,25,27,29,30</t>
+  </si>
+  <si>
+    <t>22,24,25,29,30</t>
+  </si>
+  <si>
+    <t>31,33</t>
+  </si>
+  <si>
+    <t>31,32,33,34,35,37,39,40</t>
+  </si>
+  <si>
+    <t>韧性倍率</t>
+  </si>
+  <si>
+    <t>32,34,35,39,40</t>
+  </si>
+  <si>
+    <t>增伤倍率</t>
+  </si>
+  <si>
+    <t>41,43</t>
+  </si>
+  <si>
+    <t>幸运增幅</t>
+  </si>
+  <si>
+    <t>暴击增幅</t>
+  </si>
+  <si>
+    <t>49,50</t>
+  </si>
+  <si>
+    <t>41,42,43,44,45,47,49,50</t>
+  </si>
+  <si>
+    <t>42,44,45,49,50</t>
+  </si>
+  <si>
+    <t>神话攻击</t>
+  </si>
+  <si>
+    <t>1,4,7,10</t>
+  </si>
+  <si>
+    <t>神话防御</t>
+  </si>
+  <si>
+    <t>2,5,8,11</t>
+  </si>
+  <si>
+    <t>神话生命</t>
+  </si>
+  <si>
+    <t>3,6,9,12</t>
+  </si>
+  <si>
+    <t>物理倍率</t>
+  </si>
+  <si>
+    <t>物伤倍率</t>
+  </si>
+  <si>
+    <t>法伤倍率</t>
+  </si>
+  <si>
+    <t>道伤倍率</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
   </si>
 </sst>
 </file>
@@ -861,6 +961,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1180,22 +1282,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:O65"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="C3:L70"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="8.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="19.625" style="1" customWidth="1"/>
     <col min="7" max="8" width="13" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.625" style="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.625" style="1" customWidth="1"/>
-    <col min="13" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="19.25" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="10" max="12" width="13" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.25" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:15">
+    <row r="3" ht="13.5" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1226,28 +1326,19 @@
       <c r="L3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="2" t="s">
+    </row>
+    <row r="4" ht="13.5" spans="3:12">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="3:15">
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>4</v>
@@ -1267,58 +1358,40 @@
       <c r="L4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="2" t="s">
+    </row>
+    <row r="5" ht="13.5" spans="3:12">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="3:15">
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="3:15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="3:12">
       <c r="C6" s="1">
         <v>701</v>
       </c>
@@ -1329,7 +1402,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1338,28 +1411,19 @@
         <v>2</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="L6" s="1">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1">
-        <v>5</v>
-      </c>
-      <c r="N6" s="1">
-        <v>6</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:12">
       <c r="C7" s="1">
         <v>702</v>
       </c>
@@ -1370,7 +1434,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1379,28 +1443,19 @@
         <v>3</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J7" s="1">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>140</v>
+        <v>6</v>
       </c>
       <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1">
-        <v>5</v>
-      </c>
-      <c r="N7" s="1">
-        <v>6</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:12">
       <c r="C8" s="1">
         <v>703</v>
       </c>
@@ -1411,7 +1466,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1">
         <v>2</v>
@@ -1420,28 +1475,19 @@
         <v>4</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J8" s="1">
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1">
-        <v>210</v>
+        <v>6</v>
       </c>
       <c r="L8" s="1">
-        <v>1</v>
-      </c>
-      <c r="M8" s="1">
-        <v>5</v>
-      </c>
-      <c r="N8" s="1">
-        <v>6</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:12">
       <c r="C9" s="1">
         <v>704</v>
       </c>
@@ -1452,7 +1498,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G9" s="1">
         <v>2</v>
@@ -1461,28 +1507,19 @@
         <v>5</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J9" s="1">
-        <v>211</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>280</v>
+        <v>6</v>
       </c>
       <c r="L9" s="1">
-        <v>1</v>
-      </c>
-      <c r="M9" s="1">
-        <v>5</v>
-      </c>
-      <c r="N9" s="1">
-        <v>6</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:12">
       <c r="C10" s="1">
         <v>705</v>
       </c>
@@ -1493,7 +1530,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
@@ -1502,28 +1539,19 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J10" s="1">
-        <v>281</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="L10" s="1">
-        <v>1</v>
-      </c>
-      <c r="M10" s="1">
-        <v>5</v>
-      </c>
-      <c r="N10" s="1">
-        <v>6</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:12">
       <c r="C11" s="1">
         <v>801</v>
       </c>
@@ -1534,7 +1562,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1543,28 +1571,19 @@
         <v>5</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="L11" s="1">
-        <v>1</v>
-      </c>
-      <c r="M11" s="1">
-        <v>5</v>
-      </c>
-      <c r="N11" s="1">
-        <v>6</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:12">
       <c r="C12" s="1">
         <v>802</v>
       </c>
@@ -1575,7 +1594,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G12" s="1">
         <v>2</v>
@@ -1584,28 +1603,19 @@
         <v>10</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J12" s="1">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="L12" s="1">
-        <v>1</v>
-      </c>
-      <c r="M12" s="1">
-        <v>5</v>
-      </c>
-      <c r="N12" s="1">
-        <v>6</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:12">
       <c r="C13" s="1">
         <v>803</v>
       </c>
@@ -1616,7 +1626,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G13" s="1">
         <v>3</v>
@@ -1625,28 +1635,19 @@
         <v>15</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J13" s="1">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L13" s="1">
-        <v>1</v>
-      </c>
-      <c r="M13" s="1">
-        <v>5</v>
-      </c>
-      <c r="N13" s="1">
-        <v>6</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:12">
       <c r="C14" s="1">
         <v>804</v>
       </c>
@@ -1657,7 +1658,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1">
         <v>4</v>
@@ -1666,28 +1667,19 @@
         <v>20</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J14" s="1">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="L14" s="1">
-        <v>1</v>
-      </c>
-      <c r="M14" s="1">
-        <v>5</v>
-      </c>
-      <c r="N14" s="1">
-        <v>6</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:12">
       <c r="C15" s="1">
         <v>805</v>
       </c>
@@ -1698,7 +1690,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1">
         <v>5</v>
@@ -1707,28 +1699,19 @@
         <v>25</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J15" s="1">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="L15" s="1">
-        <v>1</v>
-      </c>
-      <c r="M15" s="1">
-        <v>5</v>
-      </c>
-      <c r="N15" s="1">
-        <v>6</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:12">
       <c r="C16" s="1">
         <v>806</v>
       </c>
@@ -1739,7 +1722,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16" s="1">
         <v>6</v>
@@ -1748,28 +1731,19 @@
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J16" s="1">
-        <v>251</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="L16" s="1">
-        <v>1</v>
-      </c>
-      <c r="M16" s="1">
-        <v>5</v>
-      </c>
-      <c r="N16" s="1">
-        <v>6</v>
-      </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:12">
       <c r="C17" s="1">
         <v>807</v>
       </c>
@@ -1780,7 +1754,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G17" s="1">
         <v>7</v>
@@ -1789,28 +1763,19 @@
         <v>35</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J17" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>350</v>
+        <v>6</v>
       </c>
       <c r="L17" s="1">
-        <v>1</v>
-      </c>
-      <c r="M17" s="1">
-        <v>5</v>
-      </c>
-      <c r="N17" s="1">
-        <v>6</v>
-      </c>
-      <c r="O17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12">
       <c r="C18" s="1">
         <v>808</v>
       </c>
@@ -1821,7 +1786,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" s="1">
         <v>8</v>
@@ -1830,112 +1795,56 @@
         <v>40</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J18" s="1">
-        <v>351</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="L18" s="1">
-        <v>1</v>
-      </c>
-      <c r="M18" s="1">
-        <v>5</v>
-      </c>
-      <c r="N18" s="1">
-        <v>6</v>
-      </c>
-      <c r="O18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12">
       <c r="C19" s="1">
+        <v>809</v>
+      </c>
+      <c r="D19" s="1">
+        <v>18</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>50</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>6</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="9:9">
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="3:12">
+      <c r="C21" s="1">
         <v>1901</v>
-      </c>
-      <c r="D19" s="1">
-        <v>19</v>
-      </c>
-      <c r="E19" s="1">
-        <v>2</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="1">
-        <v>1</v>
-      </c>
-      <c r="H19" s="1">
-        <v>5</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <v>50</v>
-      </c>
-      <c r="L19" s="1">
-        <v>1</v>
-      </c>
-      <c r="M19" s="1">
-        <v>5</v>
-      </c>
-      <c r="N19" s="1">
-        <v>6</v>
-      </c>
-      <c r="O19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="3:15">
-      <c r="C20" s="1">
-        <v>1902</v>
-      </c>
-      <c r="D20" s="1">
-        <v>19</v>
-      </c>
-      <c r="E20" s="1">
-        <v>2</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="1">
-        <v>2</v>
-      </c>
-      <c r="H20" s="1">
-        <v>10</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="1">
-        <v>51</v>
-      </c>
-      <c r="K20" s="1">
-        <v>100</v>
-      </c>
-      <c r="L20" s="1">
-        <v>1</v>
-      </c>
-      <c r="M20" s="1">
-        <v>5</v>
-      </c>
-      <c r="N20" s="1">
-        <v>6</v>
-      </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:15">
-      <c r="C21" s="1">
-        <v>1903</v>
       </c>
       <c r="D21" s="1">
         <v>19</v>
@@ -1944,39 +1853,30 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G21" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J21" s="1">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L21" s="1">
-        <v>1</v>
-      </c>
-      <c r="M21" s="1">
-        <v>5</v>
-      </c>
-      <c r="N21" s="1">
-        <v>6</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12">
       <c r="C22" s="1">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="D22" s="1">
         <v>19</v>
@@ -1985,39 +1885,30 @@
         <v>2</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G22" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J22" s="1">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="K22" s="1">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="L22" s="1">
-        <v>1</v>
-      </c>
-      <c r="M22" s="1">
-        <v>5</v>
-      </c>
-      <c r="N22" s="1">
-        <v>6</v>
-      </c>
-      <c r="O22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12">
       <c r="C23" s="1">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="D23" s="1">
         <v>19</v>
@@ -2026,39 +1917,30 @@
         <v>2</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G23" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H23" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J23" s="1">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="L23" s="1">
-        <v>1</v>
-      </c>
-      <c r="M23" s="1">
-        <v>5</v>
-      </c>
-      <c r="N23" s="1">
-        <v>6</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12">
       <c r="C24" s="1">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="D24" s="1">
         <v>19</v>
@@ -2067,39 +1949,30 @@
         <v>2</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G24" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H24" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J24" s="1">
-        <v>251</v>
+        <v>1</v>
       </c>
       <c r="K24" s="1">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="L24" s="1">
-        <v>1</v>
-      </c>
-      <c r="M24" s="1">
-        <v>5</v>
-      </c>
-      <c r="N24" s="1">
-        <v>6</v>
-      </c>
-      <c r="O24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12">
       <c r="C25" s="1">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="D25" s="1">
         <v>19</v>
@@ -2108,39 +1981,30 @@
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G25" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H25" s="1">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J25" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="K25" s="1">
-        <v>350</v>
+        <v>6</v>
       </c>
       <c r="L25" s="1">
-        <v>1</v>
-      </c>
-      <c r="M25" s="1">
-        <v>5</v>
-      </c>
-      <c r="N25" s="1">
-        <v>6</v>
-      </c>
-      <c r="O25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12">
       <c r="C26" s="1">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="D26" s="1">
         <v>19</v>
@@ -2149,203 +2013,129 @@
         <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G26" s="1">
+        <v>6</v>
+      </c>
+      <c r="H26" s="1">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1</v>
+      </c>
+      <c r="K26" s="1">
+        <v>6</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12">
+      <c r="C27" s="1">
+        <v>1907</v>
+      </c>
+      <c r="D27" s="1">
+        <v>19</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="1">
+        <v>7</v>
+      </c>
+      <c r="H27" s="1">
+        <v>35</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>6</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12">
+      <c r="C28" s="1">
+        <v>1908</v>
+      </c>
+      <c r="D28" s="1">
+        <v>19</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="1">
         <v>8</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H28" s="1">
         <v>40</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J26" s="1">
-        <v>351</v>
-      </c>
-      <c r="K26" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L26" s="1">
-        <v>1</v>
-      </c>
-      <c r="M26" s="1">
-        <v>5</v>
-      </c>
-      <c r="N26" s="1">
-        <v>6</v>
-      </c>
-      <c r="O26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:15">
-      <c r="C27" s="1">
+      <c r="I28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1">
+        <v>6</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12">
+      <c r="C29" s="1">
+        <v>1909</v>
+      </c>
+      <c r="D29" s="1">
+        <v>19</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>50</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1">
+        <v>6</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="9:9">
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="3:12">
+      <c r="C31" s="1">
         <v>2001</v>
-      </c>
-      <c r="D27" s="1">
-        <v>20</v>
-      </c>
-      <c r="E27" s="1">
-        <v>2</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G27" s="1">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1">
-        <v>5</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J27" s="1">
-        <v>0</v>
-      </c>
-      <c r="K27" s="1">
-        <v>50</v>
-      </c>
-      <c r="L27" s="1">
-        <v>1</v>
-      </c>
-      <c r="M27" s="1">
-        <v>5</v>
-      </c>
-      <c r="N27" s="1">
-        <v>6</v>
-      </c>
-      <c r="O27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:15">
-      <c r="C28" s="1">
-        <v>2002</v>
-      </c>
-      <c r="D28" s="1">
-        <v>20</v>
-      </c>
-      <c r="E28" s="1">
-        <v>2</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" s="1">
-        <v>2</v>
-      </c>
-      <c r="H28" s="1">
-        <v>10</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" s="1">
-        <v>51</v>
-      </c>
-      <c r="K28" s="1">
-        <v>100</v>
-      </c>
-      <c r="L28" s="1">
-        <v>1</v>
-      </c>
-      <c r="M28" s="1">
-        <v>5</v>
-      </c>
-      <c r="N28" s="1">
-        <v>6</v>
-      </c>
-      <c r="O28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:15">
-      <c r="C29" s="1">
-        <v>2003</v>
-      </c>
-      <c r="D29" s="1">
-        <v>20</v>
-      </c>
-      <c r="E29" s="1">
-        <v>2</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29" s="1">
-        <v>3</v>
-      </c>
-      <c r="H29" s="1">
-        <v>15</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J29" s="1">
-        <v>101</v>
-      </c>
-      <c r="K29" s="1">
-        <v>150</v>
-      </c>
-      <c r="L29" s="1">
-        <v>1</v>
-      </c>
-      <c r="M29" s="1">
-        <v>5</v>
-      </c>
-      <c r="N29" s="1">
-        <v>6</v>
-      </c>
-      <c r="O29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:15">
-      <c r="C30" s="1">
-        <v>2004</v>
-      </c>
-      <c r="D30" s="1">
-        <v>20</v>
-      </c>
-      <c r="E30" s="1">
-        <v>2</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G30" s="1">
-        <v>4</v>
-      </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J30" s="1">
-        <v>151</v>
-      </c>
-      <c r="K30" s="1">
-        <v>200</v>
-      </c>
-      <c r="L30" s="1">
-        <v>1</v>
-      </c>
-      <c r="M30" s="1">
-        <v>5</v>
-      </c>
-      <c r="N30" s="1">
-        <v>6</v>
-      </c>
-      <c r="O30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="3:15">
-      <c r="C31" s="1">
-        <v>2005</v>
       </c>
       <c r="D31" s="1">
         <v>20</v>
@@ -2354,39 +2144,30 @@
         <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G31" s="1">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1">
         <v>5</v>
       </c>
-      <c r="H31" s="1">
-        <v>25</v>
-      </c>
       <c r="I31" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J31" s="1">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="L31" s="1">
-        <v>1</v>
-      </c>
-      <c r="M31" s="1">
-        <v>5</v>
-      </c>
-      <c r="N31" s="1">
-        <v>6</v>
-      </c>
-      <c r="O31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12">
       <c r="C32" s="1">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="D32" s="1">
         <v>20</v>
@@ -2395,39 +2176,30 @@
         <v>2</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G32" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H32" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J32" s="1">
-        <v>251</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="L32" s="1">
-        <v>1</v>
-      </c>
-      <c r="M32" s="1">
-        <v>5</v>
-      </c>
-      <c r="N32" s="1">
-        <v>6</v>
-      </c>
-      <c r="O32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:12">
       <c r="C33" s="1">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="D33" s="1">
         <v>20</v>
@@ -2436,39 +2208,30 @@
         <v>2</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G33" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H33" s="1">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J33" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="K33" s="1">
-        <v>350</v>
+        <v>6</v>
       </c>
       <c r="L33" s="1">
-        <v>1</v>
-      </c>
-      <c r="M33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="1">
-        <v>6</v>
-      </c>
-      <c r="O33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:12">
       <c r="C34" s="1">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="D34" s="1">
         <v>20</v>
@@ -2477,203 +2240,158 @@
         <v>2</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G34" s="1">
+        <v>4</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1">
+        <v>6</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:12">
+      <c r="C35" s="1">
+        <v>2005</v>
+      </c>
+      <c r="D35" s="1">
+        <v>20</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="1">
+        <v>5</v>
+      </c>
+      <c r="H35" s="1">
+        <v>25</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1">
+        <v>6</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:12">
+      <c r="C36" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D36" s="1">
+        <v>20</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="1">
+        <v>6</v>
+      </c>
+      <c r="H36" s="1">
+        <v>30</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1</v>
+      </c>
+      <c r="K36" s="1">
+        <v>6</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:12">
+      <c r="C37" s="1">
+        <v>2007</v>
+      </c>
+      <c r="D37" s="1">
+        <v>20</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="1">
+        <v>7</v>
+      </c>
+      <c r="H37" s="1">
+        <v>35</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1</v>
+      </c>
+      <c r="K37" s="1">
+        <v>6</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="3:12">
+      <c r="C38" s="1">
+        <v>2008</v>
+      </c>
+      <c r="D38" s="1">
+        <v>20</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="1">
         <v>8</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H38" s="1">
         <v>40</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J34" s="1">
-        <v>351</v>
-      </c>
-      <c r="K34" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L34" s="1">
-        <v>1</v>
-      </c>
-      <c r="M34" s="1">
-        <v>5</v>
-      </c>
-      <c r="N34" s="1">
-        <v>6</v>
-      </c>
-      <c r="O34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="3:15">
-      <c r="C35" s="1">
+      <c r="I38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1">
+        <v>6</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="3:12">
+      <c r="C39" s="1">
         <v>2401</v>
-      </c>
-      <c r="D35" s="1">
-        <v>24</v>
-      </c>
-      <c r="E35" s="1">
-        <v>2</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" s="1">
-        <v>1</v>
-      </c>
-      <c r="H35" s="1">
-        <v>5</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J35" s="1">
-        <v>0</v>
-      </c>
-      <c r="K35" s="1">
-        <v>50</v>
-      </c>
-      <c r="L35" s="1">
-        <v>1</v>
-      </c>
-      <c r="M35" s="1">
-        <v>5</v>
-      </c>
-      <c r="N35" s="1">
-        <v>6</v>
-      </c>
-      <c r="O35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="3:15">
-      <c r="C36" s="1">
-        <v>2402</v>
-      </c>
-      <c r="D36" s="1">
-        <v>24</v>
-      </c>
-      <c r="E36" s="1">
-        <v>2</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G36" s="1">
-        <v>2</v>
-      </c>
-      <c r="H36" s="1">
-        <v>10</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J36" s="1">
-        <v>51</v>
-      </c>
-      <c r="K36" s="1">
-        <v>100</v>
-      </c>
-      <c r="L36" s="1">
-        <v>1</v>
-      </c>
-      <c r="M36" s="1">
-        <v>5</v>
-      </c>
-      <c r="N36" s="1">
-        <v>6</v>
-      </c>
-      <c r="O36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="3:15">
-      <c r="C37" s="1">
-        <v>2403</v>
-      </c>
-      <c r="D37" s="1">
-        <v>24</v>
-      </c>
-      <c r="E37" s="1">
-        <v>2</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G37" s="1">
-        <v>3</v>
-      </c>
-      <c r="H37" s="1">
-        <v>15</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J37" s="1">
-        <v>101</v>
-      </c>
-      <c r="K37" s="1">
-        <v>150</v>
-      </c>
-      <c r="L37" s="1">
-        <v>1</v>
-      </c>
-      <c r="M37" s="1">
-        <v>5</v>
-      </c>
-      <c r="N37" s="1">
-        <v>6</v>
-      </c>
-      <c r="O37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="3:15">
-      <c r="C38" s="1">
-        <v>2404</v>
-      </c>
-      <c r="D38" s="1">
-        <v>24</v>
-      </c>
-      <c r="E38" s="1">
-        <v>2</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" s="1">
-        <v>4</v>
-      </c>
-      <c r="H38" s="1">
-        <v>20</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J38" s="1">
-        <v>151</v>
-      </c>
-      <c r="K38" s="1">
-        <v>200</v>
-      </c>
-      <c r="L38" s="1">
-        <v>1</v>
-      </c>
-      <c r="M38" s="1">
-        <v>5</v>
-      </c>
-      <c r="N38" s="1">
-        <v>6</v>
-      </c>
-      <c r="O38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="3:15">
-      <c r="C39" s="1">
-        <v>2405</v>
       </c>
       <c r="D39" s="1">
         <v>24</v>
@@ -2682,39 +2400,30 @@
         <v>2</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G39" s="1">
+        <v>1</v>
+      </c>
+      <c r="H39" s="1">
         <v>5</v>
       </c>
-      <c r="H39" s="1">
-        <v>25</v>
-      </c>
       <c r="I39" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J39" s="1">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="K39" s="1">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="L39" s="1">
-        <v>1</v>
-      </c>
-      <c r="M39" s="1">
-        <v>5</v>
-      </c>
-      <c r="N39" s="1">
-        <v>6</v>
-      </c>
-      <c r="O39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="3:12">
       <c r="C40" s="1">
-        <v>2406</v>
+        <v>2402</v>
       </c>
       <c r="D40" s="1">
         <v>24</v>
@@ -2723,39 +2432,30 @@
         <v>2</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G40" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H40" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J40" s="1">
-        <v>251</v>
+        <v>1</v>
       </c>
       <c r="K40" s="1">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="L40" s="1">
-        <v>1</v>
-      </c>
-      <c r="M40" s="1">
-        <v>5</v>
-      </c>
-      <c r="N40" s="1">
-        <v>6</v>
-      </c>
-      <c r="O40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="3:12">
       <c r="C41" s="1">
-        <v>2407</v>
+        <v>2403</v>
       </c>
       <c r="D41" s="1">
         <v>24</v>
@@ -2764,39 +2464,30 @@
         <v>2</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G41" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H41" s="1">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J41" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="K41" s="1">
-        <v>350</v>
+        <v>6</v>
       </c>
       <c r="L41" s="1">
-        <v>1</v>
-      </c>
-      <c r="M41" s="1">
-        <v>5</v>
-      </c>
-      <c r="N41" s="1">
-        <v>6</v>
-      </c>
-      <c r="O41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="3:12">
       <c r="C42" s="1">
-        <v>2408</v>
+        <v>2404</v>
       </c>
       <c r="D42" s="1">
         <v>24</v>
@@ -2805,244 +2496,190 @@
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" s="1">
+        <v>4</v>
+      </c>
+      <c r="H42" s="1">
+        <v>20</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1</v>
+      </c>
+      <c r="K42" s="1">
+        <v>6</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="3:12">
+      <c r="C43" s="1">
+        <v>2405</v>
+      </c>
+      <c r="D43" s="1">
         <v>24</v>
       </c>
-      <c r="G42" s="1">
+      <c r="E43" s="1">
+        <v>2</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" s="1">
+        <v>5</v>
+      </c>
+      <c r="H43" s="1">
+        <v>25</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+      <c r="K43" s="1">
+        <v>6</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="3:12">
+      <c r="C44" s="1">
+        <v>2406</v>
+      </c>
+      <c r="D44" s="1">
+        <v>24</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" s="1">
+        <v>6</v>
+      </c>
+      <c r="H44" s="1">
+        <v>30</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="1">
+        <v>6</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="3:12">
+      <c r="C45" s="1">
+        <v>2407</v>
+      </c>
+      <c r="D45" s="1">
+        <v>24</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="1">
+        <v>7</v>
+      </c>
+      <c r="H45" s="1">
+        <v>35</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1</v>
+      </c>
+      <c r="K45" s="1">
+        <v>6</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="3:12">
+      <c r="C46" s="1">
+        <v>2408</v>
+      </c>
+      <c r="D46" s="1">
+        <v>24</v>
+      </c>
+      <c r="E46" s="1">
+        <v>2</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="1">
         <v>8</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H46" s="1">
         <v>40</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="I46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1">
+        <v>6</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:12">
+      <c r="C47" s="1">
+        <v>2409</v>
+      </c>
+      <c r="D47" s="1">
+        <v>24</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J42" s="1">
-        <v>351</v>
-      </c>
-      <c r="K42" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L42" s="1">
-        <v>1</v>
-      </c>
-      <c r="M42" s="1">
-        <v>5</v>
-      </c>
-      <c r="N42" s="1">
-        <v>6</v>
-      </c>
-      <c r="O42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="3:15">
-      <c r="C44" s="1">
+      <c r="G47" s="1">
+        <v>10</v>
+      </c>
+      <c r="H47" s="1">
+        <v>50</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1">
+        <v>6</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12">
+      <c r="C49" s="1">
         <v>2601</v>
-      </c>
-      <c r="D44" s="1">
-        <v>26</v>
-      </c>
-      <c r="E44" s="1">
-        <v>2</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G44" s="1">
-        <v>1</v>
-      </c>
-      <c r="H44" s="1">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J44" s="1">
-        <v>0</v>
-      </c>
-      <c r="K44" s="1">
-        <v>100</v>
-      </c>
-      <c r="L44" s="1">
-        <v>1</v>
-      </c>
-      <c r="M44" s="3">
-        <v>4</v>
-      </c>
-      <c r="N44" s="3">
-        <v>6</v>
-      </c>
-      <c r="O44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="3:15">
-      <c r="C45" s="1">
-        <v>2602</v>
-      </c>
-      <c r="D45" s="1">
-        <v>26</v>
-      </c>
-      <c r="E45" s="1">
-        <v>2</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G45" s="1">
-        <v>1</v>
-      </c>
-      <c r="H45" s="1">
-        <v>4</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J45" s="1">
-        <v>101</v>
-      </c>
-      <c r="K45" s="1">
-        <v>200</v>
-      </c>
-      <c r="L45" s="1">
-        <v>1</v>
-      </c>
-      <c r="M45" s="3">
-        <v>4</v>
-      </c>
-      <c r="N45" s="3">
-        <v>6</v>
-      </c>
-      <c r="O45" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="3:15">
-      <c r="C46" s="1">
-        <v>2603</v>
-      </c>
-      <c r="D46" s="1">
-        <v>26</v>
-      </c>
-      <c r="E46" s="1">
-        <v>2</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G46" s="1">
-        <v>1</v>
-      </c>
-      <c r="H46" s="1">
-        <v>5</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J46" s="1">
-        <v>201</v>
-      </c>
-      <c r="K46" s="1">
-        <v>300</v>
-      </c>
-      <c r="L46" s="1">
-        <v>1</v>
-      </c>
-      <c r="M46" s="3">
-        <v>4</v>
-      </c>
-      <c r="N46" s="3">
-        <v>6</v>
-      </c>
-      <c r="O46" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="3:15">
-      <c r="C47" s="1">
-        <v>2604</v>
-      </c>
-      <c r="D47" s="1">
-        <v>26</v>
-      </c>
-      <c r="E47" s="1">
-        <v>2</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G47" s="1">
-        <v>1</v>
-      </c>
-      <c r="H47" s="1">
-        <v>5</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J47" s="1">
-        <v>301</v>
-      </c>
-      <c r="K47" s="1">
-        <v>400</v>
-      </c>
-      <c r="L47" s="1">
-        <v>1</v>
-      </c>
-      <c r="M47" s="3">
-        <v>4</v>
-      </c>
-      <c r="N47" s="3">
-        <v>6</v>
-      </c>
-      <c r="O47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="3:15">
-      <c r="C48" s="1">
-        <v>2605</v>
-      </c>
-      <c r="D48" s="1">
-        <v>26</v>
-      </c>
-      <c r="E48" s="1">
-        <v>2</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G48" s="1">
-        <v>1</v>
-      </c>
-      <c r="H48" s="1">
-        <v>5</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J48" s="1">
-        <v>401</v>
-      </c>
-      <c r="K48" s="1">
-        <v>500</v>
-      </c>
-      <c r="L48" s="1">
-        <v>1</v>
-      </c>
-      <c r="M48" s="3">
-        <v>4</v>
-      </c>
-      <c r="N48" s="3">
-        <v>6</v>
-      </c>
-      <c r="O48" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:15">
-      <c r="C49" s="1">
-        <v>2606</v>
       </c>
       <c r="D49" s="1">
         <v>26</v>
@@ -3051,133 +2688,135 @@
         <v>2</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
       </c>
       <c r="H49" s="1">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="3">
+        <v>6</v>
+      </c>
+      <c r="L49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12">
+      <c r="C50" s="1">
+        <v>2602</v>
+      </c>
+      <c r="D50" s="1">
+        <v>26</v>
+      </c>
+      <c r="E50" s="1">
+        <v>2</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1</v>
+      </c>
+      <c r="H50" s="1">
+        <v>4</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="3">
+        <v>6</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12">
+      <c r="C51" s="1">
+        <v>2603</v>
+      </c>
+      <c r="D51" s="1">
+        <v>26</v>
+      </c>
+      <c r="E51" s="1">
+        <v>2</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51" s="1">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1">
         <v>5</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J49" s="1">
-        <v>501</v>
-      </c>
-      <c r="K49" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L49" s="1">
-        <v>1</v>
-      </c>
-      <c r="M49" s="3">
-        <v>4</v>
-      </c>
-      <c r="N49" s="3">
-        <v>6</v>
-      </c>
-      <c r="O49" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="9:9">
-      <c r="I50" s="3"/>
-    </row>
-    <row r="51" spans="3:15">
-      <c r="C51" s="1">
-        <v>2701</v>
-      </c>
-      <c r="D51" s="1">
-        <v>27</v>
-      </c>
-      <c r="E51" s="1">
-        <v>2</v>
-      </c>
-      <c r="F51" s="1" t="s">
+      <c r="I51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="3">
+        <v>6</v>
+      </c>
+      <c r="L51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12">
+      <c r="C52" s="1">
+        <v>2604</v>
+      </c>
+      <c r="D52" s="1">
         <v>26</v>
       </c>
-      <c r="G51" s="1">
-        <v>1</v>
-      </c>
-      <c r="H51" s="1">
-        <v>3</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J51" s="1">
-        <v>0</v>
-      </c>
-      <c r="K51" s="1">
-        <v>100</v>
-      </c>
-      <c r="L51" s="1">
-        <v>1</v>
-      </c>
-      <c r="M51" s="3">
-        <v>4</v>
-      </c>
-      <c r="N51" s="3">
-        <v>6</v>
-      </c>
-      <c r="O51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="3:15">
-      <c r="C52" s="1">
-        <v>2702</v>
-      </c>
-      <c r="D52" s="1">
-        <v>27</v>
-      </c>
       <c r="E52" s="1">
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="1">
+        <v>1</v>
+      </c>
+      <c r="K52" s="3">
+        <v>6</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12">
+      <c r="C53" s="1">
+        <v>2605</v>
+      </c>
+      <c r="D53" s="1">
         <v>26</v>
       </c>
-      <c r="G52" s="1">
-        <v>1</v>
-      </c>
-      <c r="H52" s="1">
-        <v>4</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J52" s="1">
-        <v>101</v>
-      </c>
-      <c r="K52" s="1">
-        <v>200</v>
-      </c>
-      <c r="L52" s="1">
-        <v>1</v>
-      </c>
-      <c r="M52" s="3">
-        <v>4</v>
-      </c>
-      <c r="N52" s="3">
-        <v>6</v>
-      </c>
-      <c r="O52" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:15">
-      <c r="C53" s="1">
-        <v>2703</v>
-      </c>
-      <c r="D53" s="1">
-        <v>27</v>
-      </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -3186,39 +2825,30 @@
         <v>5</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J53" s="1">
-        <v>201</v>
-      </c>
-      <c r="K53" s="1">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="K53" s="3">
+        <v>6</v>
       </c>
       <c r="L53" s="1">
-        <v>1</v>
-      </c>
-      <c r="M53" s="3">
-        <v>4</v>
-      </c>
-      <c r="N53" s="3">
-        <v>6</v>
-      </c>
-      <c r="O53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12">
       <c r="C54" s="1">
-        <v>2704</v>
+        <v>2606</v>
       </c>
       <c r="D54" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -3227,71 +2857,24 @@
         <v>5</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J54" s="1">
-        <v>301</v>
-      </c>
-      <c r="K54" s="1">
-        <v>400</v>
+        <v>1</v>
+      </c>
+      <c r="K54" s="3">
+        <v>6</v>
       </c>
       <c r="L54" s="1">
-        <v>1</v>
-      </c>
-      <c r="M54" s="3">
-        <v>4</v>
-      </c>
-      <c r="N54" s="3">
-        <v>6</v>
-      </c>
-      <c r="O54" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="3:15">
-      <c r="C55" s="1">
-        <v>2705</v>
-      </c>
-      <c r="D55" s="1">
-        <v>27</v>
-      </c>
-      <c r="E55" s="1">
-        <v>2</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="1">
-        <v>1</v>
-      </c>
-      <c r="H55" s="1">
-        <v>5</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J55" s="1">
-        <v>401</v>
-      </c>
-      <c r="K55" s="1">
-        <v>500</v>
-      </c>
-      <c r="L55" s="1">
-        <v>1</v>
-      </c>
-      <c r="M55" s="3">
-        <v>4</v>
-      </c>
-      <c r="N55" s="3">
-        <v>6</v>
-      </c>
-      <c r="O55" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="9:9">
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="3:12">
       <c r="C56" s="1">
-        <v>2706</v>
+        <v>2701</v>
       </c>
       <c r="D56" s="1">
         <v>27</v>
@@ -3300,130 +2883,135 @@
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
       </c>
       <c r="H56" s="1">
+        <v>3</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="1">
+        <v>1</v>
+      </c>
+      <c r="K56" s="3">
+        <v>6</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="3:12">
+      <c r="C57" s="1">
+        <v>2702</v>
+      </c>
+      <c r="D57" s="1">
+        <v>27</v>
+      </c>
+      <c r="E57" s="1">
+        <v>2</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1</v>
+      </c>
+      <c r="H57" s="1">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="1">
+        <v>1</v>
+      </c>
+      <c r="K57" s="3">
+        <v>6</v>
+      </c>
+      <c r="L57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12">
+      <c r="C58" s="1">
+        <v>2703</v>
+      </c>
+      <c r="D58" s="1">
+        <v>27</v>
+      </c>
+      <c r="E58" s="1">
+        <v>2</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58" s="1">
+        <v>1</v>
+      </c>
+      <c r="H58" s="1">
         <v>5</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J56" s="1">
-        <v>501</v>
-      </c>
-      <c r="K56" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L56" s="1">
-        <v>1</v>
-      </c>
-      <c r="M56" s="3">
-        <v>4</v>
-      </c>
-      <c r="N56" s="3">
-        <v>6</v>
-      </c>
-      <c r="O56" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:15">
-      <c r="C58" s="1">
-        <v>2801</v>
-      </c>
-      <c r="D58" s="1">
-        <v>28</v>
-      </c>
-      <c r="E58" s="1">
-        <v>2</v>
-      </c>
-      <c r="F58" s="1" t="s">
+      <c r="I58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J58" s="1">
+        <v>1</v>
+      </c>
+      <c r="K58" s="3">
+        <v>6</v>
+      </c>
+      <c r="L58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12">
+      <c r="C59" s="1">
+        <v>2704</v>
+      </c>
+      <c r="D59" s="1">
         <v>27</v>
       </c>
-      <c r="G58" s="1">
-        <v>1</v>
-      </c>
-      <c r="H58" s="1">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J58" s="1">
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
-        <v>100</v>
-      </c>
-      <c r="L58" s="1">
-        <v>1</v>
-      </c>
-      <c r="M58" s="3">
-        <v>4</v>
-      </c>
-      <c r="N58" s="3">
-        <v>6</v>
-      </c>
-      <c r="O58" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:15">
-      <c r="C59" s="1">
-        <v>2802</v>
-      </c>
-      <c r="D59" s="1">
-        <v>28</v>
-      </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
       <c r="F59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="1">
+        <v>1</v>
+      </c>
+      <c r="H59" s="1">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1</v>
+      </c>
+      <c r="K59" s="3">
+        <v>6</v>
+      </c>
+      <c r="L59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12">
+      <c r="C60" s="1">
+        <v>2705</v>
+      </c>
+      <c r="D60" s="1">
         <v>27</v>
       </c>
-      <c r="G59" s="1">
-        <v>1</v>
-      </c>
-      <c r="H59" s="1">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J59" s="1">
-        <v>101</v>
-      </c>
-      <c r="K59" s="1">
-        <v>200</v>
-      </c>
-      <c r="L59" s="1">
-        <v>1</v>
-      </c>
-      <c r="M59" s="3">
-        <v>4</v>
-      </c>
-      <c r="N59" s="3">
-        <v>6</v>
-      </c>
-      <c r="O59" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:15">
-      <c r="C60" s="1">
-        <v>2803</v>
-      </c>
-      <c r="D60" s="1">
-        <v>28</v>
-      </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -3432,39 +3020,30 @@
         <v>5</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J60" s="1">
-        <v>201</v>
-      </c>
-      <c r="K60" s="1">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="K60" s="3">
+        <v>6</v>
       </c>
       <c r="L60" s="1">
-        <v>1</v>
-      </c>
-      <c r="M60" s="3">
-        <v>4</v>
-      </c>
-      <c r="N60" s="3">
-        <v>6</v>
-      </c>
-      <c r="O60" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12">
       <c r="C61" s="1">
-        <v>2804</v>
+        <v>2706</v>
       </c>
       <c r="D61" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -3473,71 +3052,21 @@
         <v>5</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J61" s="1">
-        <v>301</v>
-      </c>
-      <c r="K61" s="1">
-        <v>400</v>
+        <v>1</v>
+      </c>
+      <c r="K61" s="3">
+        <v>6</v>
       </c>
       <c r="L61" s="1">
-        <v>1</v>
-      </c>
-      <c r="M61" s="3">
-        <v>4</v>
-      </c>
-      <c r="N61" s="3">
-        <v>6</v>
-      </c>
-      <c r="O61" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:15">
-      <c r="C62" s="1">
-        <v>2805</v>
-      </c>
-      <c r="D62" s="1">
-        <v>28</v>
-      </c>
-      <c r="E62" s="1">
-        <v>2</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G62" s="1">
-        <v>1</v>
-      </c>
-      <c r="H62" s="1">
-        <v>5</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J62" s="1">
-        <v>401</v>
-      </c>
-      <c r="K62" s="1">
-        <v>500</v>
-      </c>
-      <c r="L62" s="1">
-        <v>1</v>
-      </c>
-      <c r="M62" s="3">
-        <v>4</v>
-      </c>
-      <c r="N62" s="3">
-        <v>6</v>
-      </c>
-      <c r="O62" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12">
       <c r="C63" s="1">
-        <v>2806</v>
+        <v>2801</v>
       </c>
       <c r="D63" s="1">
         <v>28</v>
@@ -3546,40 +3075,191 @@
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
       </c>
       <c r="H63" s="1">
+        <v>3</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J63" s="1">
+        <v>1</v>
+      </c>
+      <c r="K63" s="3">
+        <v>6</v>
+      </c>
+      <c r="L63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12">
+      <c r="C64" s="1">
+        <v>2802</v>
+      </c>
+      <c r="D64" s="1">
+        <v>28</v>
+      </c>
+      <c r="E64" s="1">
+        <v>2</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1</v>
+      </c>
+      <c r="H64" s="1">
+        <v>4</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J64" s="1">
+        <v>1</v>
+      </c>
+      <c r="K64" s="3">
+        <v>6</v>
+      </c>
+      <c r="L64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="3:12">
+      <c r="C65" s="1">
+        <v>2803</v>
+      </c>
+      <c r="D65" s="1">
+        <v>28</v>
+      </c>
+      <c r="E65" s="1">
+        <v>2</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1">
         <v>5</v>
       </c>
-      <c r="I63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J63" s="1">
-        <v>501</v>
-      </c>
-      <c r="K63" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L63" s="1">
-        <v>1</v>
-      </c>
-      <c r="M63" s="3">
-        <v>4</v>
-      </c>
-      <c r="N63" s="3">
-        <v>6</v>
-      </c>
-      <c r="O63" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1"/>
+      <c r="I65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J65" s="1">
+        <v>1</v>
+      </c>
+      <c r="K65" s="3">
+        <v>6</v>
+      </c>
+      <c r="L65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="3:12">
+      <c r="C66" s="1">
+        <v>2804</v>
+      </c>
+      <c r="D66" s="1">
+        <v>28</v>
+      </c>
+      <c r="E66" s="1">
+        <v>2</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+      <c r="H66" s="1">
+        <v>5</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1</v>
+      </c>
+      <c r="K66" s="3">
+        <v>6</v>
+      </c>
+      <c r="L66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="3:12">
+      <c r="C67" s="1">
+        <v>2805</v>
+      </c>
+      <c r="D67" s="1">
+        <v>28</v>
+      </c>
+      <c r="E67" s="1">
+        <v>2</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G67" s="1">
+        <v>1</v>
+      </c>
+      <c r="H67" s="1">
+        <v>5</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="1">
+        <v>1</v>
+      </c>
+      <c r="K67" s="3">
+        <v>6</v>
+      </c>
+      <c r="L67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="3:12">
+      <c r="C68" s="1">
+        <v>2806</v>
+      </c>
+      <c r="D68" s="1">
+        <v>28</v>
+      </c>
+      <c r="E68" s="1">
+        <v>2</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1</v>
+      </c>
+      <c r="H68" s="1">
+        <v>5</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="1">
+        <v>1</v>
+      </c>
+      <c r="K68" s="3">
+        <v>6</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3 D3 E3 E4:E5 F3:F5 C4:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -3593,22 +3273,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:O25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="C3:L60"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="8.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="19.625" style="1" customWidth="1"/>
     <col min="7" max="8" width="13" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.625" style="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.625" style="1" customWidth="1"/>
-    <col min="13" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="19.25" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.25" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" spans="3:15">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -3639,28 +3318,19 @@
       <c r="L3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="2" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:12">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="3:15">
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>4</v>
@@ -3680,58 +3350,40 @@
       <c r="L4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="2" t="s">
+    </row>
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:12">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="3:15">
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="3:15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="3:12">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -3742,7 +3394,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -3751,28 +3403,19 @@
         <v>8</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J6" s="1">
-        <v>750</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>1050</v>
+        <v>6</v>
       </c>
       <c r="L6" s="1">
-        <v>6</v>
-      </c>
-      <c r="M6" s="1">
-        <v>6</v>
-      </c>
-      <c r="N6" s="1">
-        <v>6</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="3:12">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -3783,7 +3426,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -3792,28 +3435,19 @@
         <v>3</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J7" s="1">
-        <v>750</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1050</v>
+        <v>2</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>6</v>
-      </c>
-      <c r="M7" s="1">
-        <v>6</v>
-      </c>
-      <c r="N7" s="3">
-        <v>1</v>
-      </c>
-      <c r="O7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="3:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="3:12">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -3824,7 +3458,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -3833,28 +3467,19 @@
         <v>3</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J8" s="1">
-        <v>750</v>
-      </c>
-      <c r="K8" s="1">
-        <v>1050</v>
+        <v>2</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1</v>
       </c>
       <c r="L8" s="1">
-        <v>6</v>
-      </c>
-      <c r="M8" s="1">
-        <v>6</v>
-      </c>
-      <c r="N8" s="3">
-        <v>1</v>
-      </c>
-      <c r="O8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="3:15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="3:12">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -3865,7 +3490,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -3874,28 +3499,19 @@
         <v>3</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J9" s="1">
-        <v>750</v>
-      </c>
-      <c r="K9" s="1">
-        <v>1050</v>
+        <v>2</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>6</v>
-      </c>
-      <c r="M9" s="1">
-        <v>6</v>
-      </c>
-      <c r="N9" s="3">
-        <v>1</v>
-      </c>
-      <c r="O9" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="3:15">
+    <row r="10" s="1" customFormat="1" spans="3:12">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -3906,7 +3522,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -3915,28 +3531,19 @@
         <v>10</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J10" s="1">
-        <v>750</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1050</v>
+        <v>2</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2</v>
       </c>
       <c r="L10" s="1">
-        <v>6</v>
-      </c>
-      <c r="M10" s="1">
-        <v>6</v>
-      </c>
-      <c r="N10" s="3">
-        <v>2</v>
-      </c>
-      <c r="O10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="3:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="3:12">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -3947,7 +3554,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G11" s="1">
         <v>5</v>
@@ -3956,28 +3563,19 @@
         <v>10</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J11" s="1">
-        <v>750</v>
-      </c>
-      <c r="K11" s="1">
-        <v>1050</v>
+        <v>2</v>
+      </c>
+      <c r="K11" s="3">
+        <v>2</v>
       </c>
       <c r="L11" s="1">
-        <v>6</v>
-      </c>
-      <c r="M11" s="1">
-        <v>6</v>
-      </c>
-      <c r="N11" s="3">
-        <v>2</v>
-      </c>
-      <c r="O11" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="3:15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="3:12">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -3988,7 +3586,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1">
         <v>5</v>
@@ -3997,28 +3595,19 @@
         <v>10</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J12" s="1">
-        <v>750</v>
-      </c>
-      <c r="K12" s="1">
-        <v>1050</v>
+        <v>2</v>
+      </c>
+      <c r="K12" s="3">
+        <v>2</v>
       </c>
       <c r="L12" s="1">
-        <v>6</v>
-      </c>
-      <c r="M12" s="1">
-        <v>6</v>
-      </c>
-      <c r="N12" s="3">
-        <v>2</v>
-      </c>
-      <c r="O12" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="3:15">
+    <row r="13" s="1" customFormat="1" spans="3:12">
       <c r="C13" s="1">
         <v>9</v>
       </c>
@@ -4029,7 +3618,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -4038,28 +3627,19 @@
         <v>3</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J13" s="1">
-        <v>750</v>
-      </c>
-      <c r="K13" s="1">
-        <v>1050</v>
+        <v>2</v>
+      </c>
+      <c r="K13" s="3">
+        <v>1</v>
       </c>
       <c r="L13" s="1">
-        <v>6</v>
-      </c>
-      <c r="M13" s="1">
-        <v>6</v>
-      </c>
-      <c r="N13" s="3">
-        <v>1</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="3:12">
       <c r="C14" s="1">
         <v>10</v>
       </c>
@@ -4070,7 +3650,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -4079,28 +3659,19 @@
         <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J14" s="1">
-        <v>750</v>
-      </c>
-      <c r="K14" s="1">
-        <v>1050</v>
+        <v>2</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1</v>
       </c>
       <c r="L14" s="1">
-        <v>6</v>
-      </c>
-      <c r="M14" s="1">
-        <v>6</v>
-      </c>
-      <c r="N14" s="3">
-        <v>1</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="3:12">
       <c r="C15" s="1">
         <v>11</v>
       </c>
@@ -4111,7 +3682,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -4120,28 +3691,19 @@
         <v>3</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J15" s="1">
-        <v>750</v>
-      </c>
-      <c r="K15" s="1">
-        <v>1050</v>
+        <v>2</v>
+      </c>
+      <c r="K15" s="3">
+        <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>6</v>
-      </c>
-      <c r="M15" s="1">
-        <v>6</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="3:12">
       <c r="C16" s="1">
         <v>12</v>
       </c>
@@ -4152,7 +3714,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16" s="1">
         <v>25</v>
@@ -4161,28 +3723,19 @@
         <v>50</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J16" s="1">
-        <v>750</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1">
-        <v>1050</v>
+        <v>6</v>
       </c>
       <c r="L16" s="1">
-        <v>6</v>
-      </c>
-      <c r="M16" s="1">
-        <v>6</v>
-      </c>
-      <c r="N16" s="1">
-        <v>6</v>
-      </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="3:12">
       <c r="C17" s="1">
         <v>13</v>
       </c>
@@ -4193,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G17" s="1">
         <v>25</v>
@@ -4202,28 +3755,19 @@
         <v>50</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J17" s="1">
-        <v>750</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1">
-        <v>1050</v>
+        <v>6</v>
       </c>
       <c r="L17" s="1">
-        <v>6</v>
-      </c>
-      <c r="M17" s="1">
-        <v>6</v>
-      </c>
-      <c r="N17" s="1">
-        <v>6</v>
-      </c>
-      <c r="O17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="3:12">
       <c r="C18" s="1">
         <v>14</v>
       </c>
@@ -4234,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G18" s="1">
         <v>25</v>
@@ -4243,28 +3787,19 @@
         <v>50</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J18" s="1">
-        <v>750</v>
+        <v>2</v>
       </c>
       <c r="K18" s="1">
-        <v>1050</v>
+        <v>6</v>
       </c>
       <c r="L18" s="1">
-        <v>6</v>
-      </c>
-      <c r="M18" s="1">
-        <v>6</v>
-      </c>
-      <c r="N18" s="1">
-        <v>6</v>
-      </c>
-      <c r="O18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="3:12">
       <c r="C19" s="1">
         <v>15</v>
       </c>
@@ -4275,7 +3810,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G19" s="1">
         <v>25</v>
@@ -4284,28 +3819,19 @@
         <v>50</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J19" s="1">
-        <v>750</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1">
-        <v>1050</v>
+        <v>6</v>
       </c>
       <c r="L19" s="1">
-        <v>6</v>
-      </c>
-      <c r="M19" s="1">
-        <v>6</v>
-      </c>
-      <c r="N19" s="1">
-        <v>6</v>
-      </c>
-      <c r="O19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="3:12">
       <c r="C20" s="1">
         <v>16</v>
       </c>
@@ -4316,58 +3842,1672 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="1">
+        <v>2</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="9:12">
+      <c r="I21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="3:12">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1">
+        <v>7</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="1">
+        <v>20</v>
+      </c>
+      <c r="H22" s="1">
+        <v>50</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="1">
+        <v>3</v>
+      </c>
+      <c r="K22" s="1">
+        <v>6</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="3:12">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="1">
+        <v>5</v>
+      </c>
+      <c r="H23" s="1">
+        <v>10</v>
+      </c>
+      <c r="I23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="1">
-        <v>1</v>
-      </c>
-      <c r="H20" s="1">
-        <v>1</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J23" s="1">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3">
+        <v>2</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="3:12">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2005</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="1">
+        <v>5</v>
+      </c>
+      <c r="H24" s="1">
+        <v>10</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J24" s="1">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>2</v>
+      </c>
+      <c r="L24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="3:12">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="1">
+        <v>5</v>
+      </c>
+      <c r="H25" s="1">
+        <v>10</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J25" s="1">
+        <v>3</v>
+      </c>
+      <c r="K25" s="3">
+        <v>2</v>
+      </c>
+      <c r="L25" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="3:12">
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1">
+        <v>33</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="1">
+        <v>20</v>
+      </c>
+      <c r="H26" s="1">
+        <v>40</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J26" s="1">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3">
+        <v>3</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="3:12">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1">
+        <v>34</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="1">
+        <v>20</v>
+      </c>
+      <c r="H27" s="1">
+        <v>40</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J27" s="1">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3">
+        <v>3</v>
+      </c>
+      <c r="L27" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="3:12">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <v>35</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28" s="1">
+        <v>20</v>
+      </c>
+      <c r="H28" s="1">
+        <v>40</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J28" s="1">
+        <v>3</v>
+      </c>
+      <c r="K28" s="3">
+        <v>3</v>
+      </c>
+      <c r="L28" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="3:12">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2001</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" s="1">
+        <v>5</v>
+      </c>
+      <c r="H29" s="1">
+        <v>10</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J29" s="1">
+        <v>3</v>
+      </c>
+      <c r="K29" s="3">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="3:12">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2002</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="1">
+        <v>5</v>
+      </c>
+      <c r="H30" s="1">
+        <v>10</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J30" s="1">
+        <v>3</v>
+      </c>
+      <c r="K30" s="3">
+        <v>3</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="3:12">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2003</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31" s="1">
+        <v>5</v>
+      </c>
+      <c r="H31" s="1">
+        <v>10</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J31" s="1">
+        <v>3</v>
+      </c>
+      <c r="K31" s="3">
+        <v>3</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="3:12">
+      <c r="C32" s="1">
+        <v>31</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2011</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" s="1">
+        <v>5</v>
+      </c>
+      <c r="H32" s="1">
+        <v>10</v>
+      </c>
+      <c r="I32" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="J20" s="1">
-        <v>750</v>
-      </c>
-      <c r="K20" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L20" s="1">
-        <v>6</v>
-      </c>
-      <c r="M20" s="1">
-        <v>6</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1</v>
-      </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="9:15">
-      <c r="I21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="9:15">
-      <c r="I22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="9:15">
-      <c r="I23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="15" customHeight="1"/>
+      <c r="J32" s="1">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:12">
+      <c r="C34" s="1">
+        <v>32</v>
+      </c>
+      <c r="D34" s="1">
+        <v>7</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="1">
+        <v>50</v>
+      </c>
+      <c r="H34" s="1">
+        <v>100</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" s="1">
+        <v>4</v>
+      </c>
+      <c r="K34" s="1">
+        <v>6</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:12">
+      <c r="C35" s="1">
+        <v>33</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" s="1">
+        <v>10</v>
+      </c>
+      <c r="H35" s="1">
+        <v>20</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J35" s="1">
+        <v>4</v>
+      </c>
+      <c r="K35" s="3">
+        <v>3</v>
+      </c>
+      <c r="L35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="3:12">
+      <c r="C36" s="1">
+        <v>34</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2005</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="1">
+        <v>10</v>
+      </c>
+      <c r="H36" s="1">
+        <v>20</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J36" s="1">
+        <v>4</v>
+      </c>
+      <c r="K36" s="3">
+        <v>3</v>
+      </c>
+      <c r="L36" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="3:12">
+      <c r="C37" s="1">
+        <v>35</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G37" s="1">
+        <v>10</v>
+      </c>
+      <c r="H37" s="1">
+        <v>20</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J37" s="1">
+        <v>4</v>
+      </c>
+      <c r="K37" s="3">
+        <v>3</v>
+      </c>
+      <c r="L37" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="3:12">
+      <c r="C38" s="1">
+        <v>36</v>
+      </c>
+      <c r="D38" s="1">
+        <v>33</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" s="1">
+        <v>40</v>
+      </c>
+      <c r="H38" s="1">
+        <v>80</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J38" s="1">
+        <v>4</v>
+      </c>
+      <c r="K38" s="3">
+        <v>4</v>
+      </c>
+      <c r="L38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="3:12">
+      <c r="C39" s="1">
+        <v>37</v>
+      </c>
+      <c r="D39" s="1">
+        <v>34</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="1">
+        <v>40</v>
+      </c>
+      <c r="H39" s="1">
+        <v>80</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J39" s="1">
+        <v>4</v>
+      </c>
+      <c r="K39" s="3">
+        <v>4</v>
+      </c>
+      <c r="L39" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="3:12">
+      <c r="C40" s="1">
+        <v>38</v>
+      </c>
+      <c r="D40" s="1">
+        <v>35</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" s="1">
+        <v>40</v>
+      </c>
+      <c r="H40" s="1">
+        <v>80</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J40" s="1">
+        <v>4</v>
+      </c>
+      <c r="K40" s="3">
+        <v>4</v>
+      </c>
+      <c r="L40" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="3:12">
+      <c r="C41" s="1">
+        <v>39</v>
+      </c>
+      <c r="D41" s="1">
+        <v>2001</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G41" s="1">
+        <v>10</v>
+      </c>
+      <c r="H41" s="1">
+        <v>20</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J41" s="1">
+        <v>4</v>
+      </c>
+      <c r="K41" s="3">
+        <v>2</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="3:12">
+      <c r="C42" s="1">
+        <v>40</v>
+      </c>
+      <c r="D42" s="1">
+        <v>2002</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G42" s="1">
+        <v>10</v>
+      </c>
+      <c r="H42" s="1">
+        <v>20</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J42" s="1">
+        <v>4</v>
+      </c>
+      <c r="K42" s="3">
+        <v>4</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="3:12">
+      <c r="C43" s="1">
+        <v>41</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2003</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" s="1">
+        <v>10</v>
+      </c>
+      <c r="H43" s="1">
+        <v>20</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J43" s="1">
+        <v>4</v>
+      </c>
+      <c r="K43" s="3">
+        <v>4</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="3:12">
+      <c r="C44" s="1">
+        <v>42</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2012</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G44" s="1">
+        <v>10</v>
+      </c>
+      <c r="H44" s="1">
+        <v>20</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J44" s="1">
+        <v>4</v>
+      </c>
+      <c r="K44" s="3">
+        <v>2</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="3:12">
+      <c r="C45" s="1">
+        <v>43</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G45" s="1">
+        <v>10</v>
+      </c>
+      <c r="H45" s="1">
+        <v>20</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J45" s="1">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
+        <v>2</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:12">
+      <c r="C47" s="1">
+        <v>44</v>
+      </c>
+      <c r="D47" s="1">
+        <v>7</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="1">
+        <v>100</v>
+      </c>
+      <c r="H47" s="1">
+        <v>200</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J47" s="1">
+        <v>5</v>
+      </c>
+      <c r="K47" s="1">
+        <v>6</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="3:12">
+      <c r="C48" s="1">
+        <v>45</v>
+      </c>
+      <c r="D48" s="1">
+        <v>55</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J48" s="1">
+        <v>5</v>
+      </c>
+      <c r="K48" s="1">
+        <v>1</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12">
+      <c r="C49" s="1">
+        <v>46</v>
+      </c>
+      <c r="D49" s="1">
+        <v>54</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+      <c r="H49" s="1">
+        <v>1</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J49" s="1">
+        <v>5</v>
+      </c>
+      <c r="K49" s="1">
+        <v>1</v>
+      </c>
+      <c r="L49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12">
+      <c r="C50" s="1">
+        <v>47</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50" s="1">
+        <v>10</v>
+      </c>
+      <c r="H50" s="1">
+        <v>30</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J50" s="1">
+        <v>5</v>
+      </c>
+      <c r="K50" s="3">
+        <v>3</v>
+      </c>
+      <c r="L50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12">
+      <c r="C51" s="1">
+        <v>48</v>
+      </c>
+      <c r="D51" s="1">
+        <v>2005</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="1">
+        <v>10</v>
+      </c>
+      <c r="H51" s="1">
+        <v>30</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J51" s="1">
+        <v>5</v>
+      </c>
+      <c r="K51" s="3">
+        <v>3</v>
+      </c>
+      <c r="L51" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12">
+      <c r="C52" s="1">
+        <v>49</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G52" s="1">
+        <v>10</v>
+      </c>
+      <c r="H52" s="1">
+        <v>30</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J52" s="1">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
+        <v>3</v>
+      </c>
+      <c r="L52" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12">
+      <c r="C53" s="1">
+        <v>50</v>
+      </c>
+      <c r="D53" s="1">
+        <v>33</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G53" s="1">
+        <v>100</v>
+      </c>
+      <c r="H53" s="1">
+        <v>200</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J53" s="1">
+        <v>5</v>
+      </c>
+      <c r="K53" s="3">
+        <v>6</v>
+      </c>
+      <c r="L53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12">
+      <c r="C54" s="1">
+        <v>51</v>
+      </c>
+      <c r="D54" s="1">
+        <v>34</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G54" s="1">
+        <v>100</v>
+      </c>
+      <c r="H54" s="1">
+        <v>200</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J54" s="1">
+        <v>5</v>
+      </c>
+      <c r="K54" s="3">
+        <v>6</v>
+      </c>
+      <c r="L54" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12">
+      <c r="C55" s="1">
+        <v>52</v>
+      </c>
+      <c r="D55" s="1">
+        <v>35</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G55" s="1">
+        <v>100</v>
+      </c>
+      <c r="H55" s="1">
+        <v>200</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J55" s="1">
+        <v>5</v>
+      </c>
+      <c r="K55" s="3">
+        <v>6</v>
+      </c>
+      <c r="L55" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="3:12">
+      <c r="C56" s="1">
+        <v>53</v>
+      </c>
+      <c r="D56" s="1">
+        <v>2001</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G56" s="1">
+        <v>10</v>
+      </c>
+      <c r="H56" s="1">
+        <v>30</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J56" s="1">
+        <v>5</v>
+      </c>
+      <c r="K56" s="3">
+        <v>2</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="3:12">
+      <c r="C57" s="1">
+        <v>54</v>
+      </c>
+      <c r="D57" s="1">
+        <v>2002</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G57" s="1">
+        <v>10</v>
+      </c>
+      <c r="H57" s="1">
+        <v>30</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J57" s="1">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
+        <v>4</v>
+      </c>
+      <c r="L57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12">
+      <c r="C58" s="1">
+        <v>55</v>
+      </c>
+      <c r="D58" s="1">
+        <v>2003</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G58" s="1">
+        <v>10</v>
+      </c>
+      <c r="H58" s="1">
+        <v>30</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J58" s="1">
+        <v>5</v>
+      </c>
+      <c r="K58" s="3">
+        <v>4</v>
+      </c>
+      <c r="L58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12">
+      <c r="C59" s="1">
+        <v>56</v>
+      </c>
+      <c r="D59" s="1">
+        <v>2012</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G59" s="1">
+        <v>10</v>
+      </c>
+      <c r="H59" s="1">
+        <v>30</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J59" s="1">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
+        <v>2</v>
+      </c>
+      <c r="L59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12">
+      <c r="C60" s="1">
+        <v>57</v>
+      </c>
+      <c r="D60" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G60" s="1">
+        <v>10</v>
+      </c>
+      <c r="H60" s="1">
+        <v>30</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J60" s="1">
+        <v>5</v>
+      </c>
+      <c r="K60" s="3">
+        <v>2</v>
+      </c>
+      <c r="L60" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3 D3 E3 E4:E5 F3:F5 C4:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C3:L17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="8.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.25" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:12">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:12">
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:12">
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="3:12">
+      <c r="C6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>91</v>
+      </c>
+      <c r="E6" s="1">
+        <v>6</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>10</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="1">
+        <v>99</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="3:12">
+      <c r="C7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>92</v>
+      </c>
+      <c r="E7" s="1">
+        <v>6</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>10</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="1">
+        <v>99</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="3:12">
+      <c r="C8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>93</v>
+      </c>
+      <c r="E8" s="1">
+        <v>6</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>10</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="1">
+        <v>99</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="3:12">
+      <c r="C9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E9" s="1">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="1">
+        <v>99</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="3:12">
+      <c r="C10" s="1">
+        <v>1005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2005</v>
+      </c>
+      <c r="E10" s="1">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="1">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="1">
+        <v>99</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="3:12">
+      <c r="C11" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E11" s="1">
+        <v>7</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="1">
+        <v>25</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="1">
+        <v>99</v>
+      </c>
+      <c r="K11" s="3">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="3:12">
+      <c r="C12" s="1">
+        <v>1007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2007</v>
+      </c>
+      <c r="E12" s="1">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="1">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" s="1">
+        <v>99</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="3:12">
+      <c r="C13" s="1">
+        <v>1008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2008</v>
+      </c>
+      <c r="E13" s="1">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="1">
+        <v>25</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="1">
+        <v>99</v>
+      </c>
+      <c r="K13" s="3">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="3:12">
+      <c r="C14" s="1">
+        <v>1009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2009</v>
+      </c>
+      <c r="E14" s="1">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="1">
+        <v>25</v>
+      </c>
+      <c r="H14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="1">
+        <v>99</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="3:12">
+      <c r="C15" s="1">
+        <v>1010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E15" s="1">
+        <v>9</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="1">
+        <v>25</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J15" s="1">
+        <v>99</v>
+      </c>
+      <c r="K15" s="3">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="11:11">
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="9:11">
+      <c r="I17" s="3"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="46">
   <si>
     <t>#</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>1,2,3,4,5,7,9,10</t>
+  </si>
+  <si>
+    <t>全技能等级增加</t>
   </si>
   <si>
     <t>生命</t>
@@ -1164,7 +1167,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N57"/>
+  <dimension ref="C1:N58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1681,59 +1684,59 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:14">
-      <c r="C17" s="1">
-        <v>101</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H17" s="3" t="s">
+    <row r="16" customHeight="1" spans="3:14">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>222</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>40</v>
-      </c>
-      <c r="K17" s="1">
-        <v>2</v>
-      </c>
-      <c r="L17" s="3">
-        <v>100</v>
-      </c>
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
-      <c r="N17" s="1" t="s">
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:14">
       <c r="C18" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
       </c>
       <c r="E18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>24</v>
@@ -1759,19 +1762,19 @@
     </row>
     <row r="19" customHeight="1" spans="3:14">
       <c r="C19" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
       </c>
       <c r="E19" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" s="1">
         <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>24</v>
@@ -1797,22 +1800,22 @@
     </row>
     <row r="20" customHeight="1" spans="3:14">
       <c r="C20" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
       </c>
       <c r="E20" s="1">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
@@ -1821,7 +1824,7 @@
         <v>40</v>
       </c>
       <c r="K20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
@@ -1835,22 +1838,22 @@
     </row>
     <row r="21" customHeight="1" spans="3:14">
       <c r="C21" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
       </c>
       <c r="E21" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H21" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
@@ -1873,22 +1876,22 @@
     </row>
     <row r="22" customHeight="1" spans="3:14">
       <c r="C22" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
       </c>
       <c r="E22" s="1">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F22" s="1">
         <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H22" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
@@ -1911,22 +1914,22 @@
     </row>
     <row r="23" customHeight="1" spans="3:14">
       <c r="C23" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
       <c r="E23" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F23" s="1">
         <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
@@ -1949,13 +1952,13 @@
     </row>
     <row r="24" customHeight="1" spans="3:14">
       <c r="C24" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="E24" s="1">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="F24" s="1">
         <v>1</v>
@@ -1963,8 +1966,8 @@
       <c r="G24" s="1">
         <v>3</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>24</v>
+      <c r="H24" s="3">
+        <v>5</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
@@ -1987,13 +1990,13 @@
     </row>
     <row r="25" customHeight="1" spans="3:14">
       <c r="C25" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
       </c>
       <c r="E25" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F25" s="1">
         <v>1</v>
@@ -2025,13 +2028,13 @@
     </row>
     <row r="26" customHeight="1" spans="3:14">
       <c r="C26" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
       </c>
       <c r="E26" s="1">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F26" s="1">
         <v>1</v>
@@ -2063,13 +2066,13 @@
     </row>
     <row r="27" customHeight="1" spans="3:14">
       <c r="C27" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
       </c>
       <c r="E27" s="1">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F27" s="1">
         <v>1</v>
@@ -2101,19 +2104,19 @@
     </row>
     <row r="28" customHeight="1" spans="3:14">
       <c r="C28" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
       </c>
       <c r="E28" s="1">
-        <v>1001</v>
+        <v>84</v>
       </c>
       <c r="F28" s="1">
         <v>1</v>
       </c>
       <c r="G28" s="1">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>24</v>
@@ -2125,7 +2128,7 @@
         <v>40</v>
       </c>
       <c r="K28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28" s="3">
         <v>100</v>
@@ -2139,19 +2142,19 @@
     </row>
     <row r="29" customHeight="1" spans="3:14">
       <c r="C29" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
       </c>
       <c r="E29" s="1">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F29" s="1">
         <v>1</v>
       </c>
       <c r="G29" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>24</v>
@@ -2177,19 +2180,19 @@
     </row>
     <row r="30" customHeight="1" spans="3:14">
       <c r="C30" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
       </c>
       <c r="E30" s="1">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F30" s="1">
         <v>1</v>
       </c>
       <c r="G30" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>24</v>
@@ -2215,19 +2218,19 @@
     </row>
     <row r="31" customHeight="1" spans="3:14">
       <c r="C31" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
       </c>
       <c r="E31" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F31" s="1">
         <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>24</v>
@@ -2245,7 +2248,7 @@
         <v>100</v>
       </c>
       <c r="M31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>39</v>
@@ -2253,13 +2256,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:14">
       <c r="C32" s="1">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F32" s="1">
         <v>1</v>
@@ -2283,7 +2286,7 @@
         <v>100</v>
       </c>
       <c r="M32" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>40</v>
@@ -2291,13 +2294,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:14">
       <c r="C33" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
       </c>
       <c r="E33" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F33" s="1">
         <v>1</v>
@@ -2321,7 +2324,7 @@
         <v>100</v>
       </c>
       <c r="M33" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>41</v>
@@ -2329,13 +2332,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:14">
       <c r="C34" s="1">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
       </c>
       <c r="E34" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F34" s="1">
         <v>1</v>
@@ -2353,13 +2356,13 @@
         <v>40</v>
       </c>
       <c r="K34" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="3">
         <v>100</v>
       </c>
       <c r="M34" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>42</v>
@@ -2367,13 +2370,13 @@
     </row>
     <row r="35" customHeight="1" spans="3:14">
       <c r="C35" s="1">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
       </c>
       <c r="E35" s="1">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F35" s="1">
         <v>1</v>
@@ -2397,21 +2400,21 @@
         <v>100</v>
       </c>
       <c r="M35" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1" spans="3:14">
+    <row r="36" customHeight="1" spans="3:14">
       <c r="C36" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D36" s="1">
         <v>1</v>
       </c>
       <c r="E36" s="1">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="F36" s="1">
         <v>1</v>
@@ -2435,70 +2438,70 @@
         <v>100</v>
       </c>
       <c r="M36" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="3:14">
-      <c r="H37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
+    <row r="37" ht="18" customHeight="1" spans="3:14">
+      <c r="C37" s="1">
+        <v>120</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1009</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1">
+        <v>8</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
+        <v>40</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="3">
+        <v>100</v>
+      </c>
+      <c r="M37" s="1">
+        <v>3</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="38" customHeight="1" spans="3:14">
-      <c r="C38" s="1">
-        <v>201</v>
-      </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1">
-        <v>1</v>
-      </c>
-      <c r="G38" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I38" s="1">
-        <v>50</v>
-      </c>
-      <c r="J38" s="1">
-        <v>90</v>
-      </c>
-      <c r="K38" s="1">
-        <v>2</v>
-      </c>
-      <c r="L38" s="3">
-        <v>100</v>
-      </c>
-      <c r="M38" s="1">
-        <v>0</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="H38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
     </row>
     <row r="39" customHeight="1" spans="3:14">
       <c r="C39" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
       </c>
       <c r="E39" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" s="1">
         <v>1</v>
       </c>
       <c r="G39" s="1">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>24</v>
@@ -2524,19 +2527,19 @@
     </row>
     <row r="40" customHeight="1" spans="3:14">
       <c r="C40" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
       </c>
       <c r="E40" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" s="1">
         <v>1</v>
       </c>
       <c r="G40" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>24</v>
@@ -2562,22 +2565,22 @@
     </row>
     <row r="41" customHeight="1" spans="3:14">
       <c r="C41" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D41" s="1">
         <v>1</v>
       </c>
       <c r="E41" s="1">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F41" s="1">
         <v>1</v>
       </c>
       <c r="G41" s="1">
-        <v>5</v>
-      </c>
-      <c r="H41" s="3">
-        <v>9</v>
+        <v>1000</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="I41" s="1">
         <v>50</v>
@@ -2586,7 +2589,7 @@
         <v>90</v>
       </c>
       <c r="K41" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="3">
         <v>100</v>
@@ -2600,22 +2603,22 @@
     </row>
     <row r="42" customHeight="1" spans="3:14">
       <c r="C42" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D42" s="1">
         <v>1</v>
       </c>
       <c r="E42" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F42" s="1">
         <v>1</v>
       </c>
       <c r="G42" s="1">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="H42" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I42" s="1">
         <v>50</v>
@@ -2638,22 +2641,22 @@
     </row>
     <row r="43" customHeight="1" spans="3:14">
       <c r="C43" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D43" s="1">
         <v>1</v>
       </c>
       <c r="E43" s="1">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F43" s="1">
         <v>1</v>
       </c>
       <c r="G43" s="1">
+        <v>40</v>
+      </c>
+      <c r="H43" s="3">
         <v>10</v>
-      </c>
-      <c r="H43" s="3">
-        <v>7</v>
       </c>
       <c r="I43" s="1">
         <v>50</v>
@@ -2676,22 +2679,22 @@
     </row>
     <row r="44" customHeight="1" spans="3:14">
       <c r="C44" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
       <c r="E44" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F44" s="1">
         <v>1</v>
       </c>
       <c r="G44" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H44" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I44" s="1">
         <v>50</v>
@@ -2714,13 +2717,13 @@
     </row>
     <row r="45" customHeight="1" spans="3:14">
       <c r="C45" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D45" s="1">
         <v>1</v>
       </c>
       <c r="E45" s="1">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="F45" s="1">
         <v>1</v>
@@ -2728,8 +2731,8 @@
       <c r="G45" s="1">
         <v>5</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>24</v>
+      <c r="H45" s="3">
+        <v>5</v>
       </c>
       <c r="I45" s="1">
         <v>50</v>
@@ -2752,13 +2755,13 @@
     </row>
     <row r="46" customHeight="1" spans="3:14">
       <c r="C46" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D46" s="1">
         <v>1</v>
       </c>
       <c r="E46" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F46" s="1">
         <v>1</v>
@@ -2790,13 +2793,13 @@
     </row>
     <row r="47" customHeight="1" spans="3:14">
       <c r="C47" s="1">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
       </c>
       <c r="E47" s="1">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F47" s="1">
         <v>1</v>
@@ -2828,13 +2831,13 @@
     </row>
     <row r="48" customHeight="1" spans="3:14">
       <c r="C48" s="1">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D48" s="1">
         <v>1</v>
       </c>
       <c r="E48" s="1">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F48" s="1">
         <v>1</v>
@@ -2866,19 +2869,19 @@
     </row>
     <row r="49" customHeight="1" spans="3:14">
       <c r="C49" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D49" s="1">
         <v>1</v>
       </c>
       <c r="E49" s="1">
-        <v>1001</v>
+        <v>84</v>
       </c>
       <c r="F49" s="1">
         <v>1</v>
       </c>
       <c r="G49" s="1">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>24</v>
@@ -2890,7 +2893,7 @@
         <v>90</v>
       </c>
       <c r="K49" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" s="3">
         <v>100</v>
@@ -2904,19 +2907,19 @@
     </row>
     <row r="50" customHeight="1" spans="3:14">
       <c r="C50" s="1">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
       </c>
       <c r="E50" s="1">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F50" s="1">
         <v>1</v>
       </c>
       <c r="G50" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>24</v>
@@ -2942,19 +2945,19 @@
     </row>
     <row r="51" customHeight="1" spans="3:14">
       <c r="C51" s="1">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D51" s="1">
         <v>1</v>
       </c>
       <c r="E51" s="1">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
       </c>
       <c r="G51" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>24</v>
@@ -2980,19 +2983,19 @@
     </row>
     <row r="52" customHeight="1" spans="3:14">
       <c r="C52" s="1">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D52" s="1">
         <v>1</v>
       </c>
       <c r="E52" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F52" s="1">
         <v>1</v>
       </c>
       <c r="G52" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>24</v>
@@ -3010,7 +3013,7 @@
         <v>100</v>
       </c>
       <c r="M52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>39</v>
@@ -3018,13 +3021,13 @@
     </row>
     <row r="53" customHeight="1" spans="3:14">
       <c r="C53" s="1">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D53" s="1">
         <v>1</v>
       </c>
       <c r="E53" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F53" s="1">
         <v>1</v>
@@ -3048,7 +3051,7 @@
         <v>100</v>
       </c>
       <c r="M53" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>40</v>
@@ -3056,13 +3059,13 @@
     </row>
     <row r="54" customHeight="1" spans="3:14">
       <c r="C54" s="1">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D54" s="1">
         <v>1</v>
       </c>
       <c r="E54" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F54" s="1">
         <v>1</v>
@@ -3086,7 +3089,7 @@
         <v>100</v>
       </c>
       <c r="M54" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>41</v>
@@ -3094,13 +3097,13 @@
     </row>
     <row r="55" customHeight="1" spans="3:14">
       <c r="C55" s="1">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D55" s="1">
         <v>1</v>
       </c>
       <c r="E55" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F55" s="1">
         <v>1</v>
@@ -3118,13 +3121,13 @@
         <v>90</v>
       </c>
       <c r="K55" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" s="3">
         <v>100</v>
       </c>
       <c r="M55" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>42</v>
@@ -3132,13 +3135,13 @@
     </row>
     <row r="56" customHeight="1" spans="3:14">
       <c r="C56" s="1">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
       </c>
       <c r="E56" s="1">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F56" s="1">
         <v>1</v>
@@ -3162,7 +3165,7 @@
         <v>100</v>
       </c>
       <c r="M56" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N56" s="1" t="s">
         <v>43</v>
@@ -3170,13 +3173,13 @@
     </row>
     <row r="57" customHeight="1" spans="3:14">
       <c r="C57" s="1">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D57" s="1">
         <v>1</v>
       </c>
       <c r="E57" s="1">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="F57" s="1">
         <v>1</v>
@@ -3200,10 +3203,48 @@
         <v>100</v>
       </c>
       <c r="M57" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N57" s="1" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:14">
+      <c r="C58" s="1">
+        <v>220</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1009</v>
+      </c>
+      <c r="F58" s="1">
+        <v>1</v>
+      </c>
+      <c r="G58" s="1">
+        <v>15</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58" s="1">
+        <v>50</v>
+      </c>
+      <c r="J58" s="1">
+        <v>90</v>
+      </c>
+      <c r="K58" s="1">
+        <v>1</v>
+      </c>
+      <c r="L58" s="3">
+        <v>100</v>
+      </c>
+      <c r="M58" s="1">
+        <v>3</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="50">
   <si>
     <t>#</t>
   </si>
@@ -116,10 +116,22 @@
     <t>string</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>幸运</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>诅咒</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>命中</t>
@@ -848,6 +860,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1318,10 +1331,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -1330,7 +1343,7 @@
         <v>99999</v>
       </c>
       <c r="K6" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L6" s="1">
         <v>30</v>
@@ -1339,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:14">
@@ -1356,10 +1369,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1">
         <v>3</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
@@ -1368,7 +1381,7 @@
         <v>99999</v>
       </c>
       <c r="K7" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L7" s="1">
         <v>30</v>
@@ -1377,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:14">
@@ -1394,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -1406,7 +1419,7 @@
         <v>99999</v>
       </c>
       <c r="K8" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L8" s="1">
         <v>30</v>
@@ -1415,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:14">
@@ -1432,10 +1445,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
@@ -1444,7 +1457,7 @@
         <v>99999</v>
       </c>
       <c r="K9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" s="1">
         <v>30</v>
@@ -1453,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:14">
@@ -1470,7 +1483,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" s="1">
         <v>9</v>
@@ -1482,7 +1495,7 @@
         <v>99999</v>
       </c>
       <c r="K10" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" s="1">
         <v>30</v>
@@ -1491,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:14">
@@ -1508,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -1520,7 +1533,7 @@
         <v>99999</v>
       </c>
       <c r="K11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" s="1">
         <v>30</v>
@@ -1529,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:14">
@@ -1567,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:14">
@@ -1605,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:14">
@@ -1643,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:14">
@@ -1681,7 +1694,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:14">
@@ -1701,7 +1714,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -1719,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:14">
@@ -1733,19 +1746,19 @@
         <v>1</v>
       </c>
       <c r="F18" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G18" s="1">
         <v>1000</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K18" s="1">
         <v>2</v>
@@ -1757,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:14">
@@ -1771,19 +1784,19 @@
         <v>2</v>
       </c>
       <c r="F19" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G19" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K19" s="1">
         <v>2</v>
@@ -1795,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:14">
@@ -1809,19 +1822,19 @@
         <v>3</v>
       </c>
       <c r="F20" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G20" s="1">
         <v>100</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K20" s="1">
         <v>2</v>
@@ -1833,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:14">
@@ -1859,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K21" s="1">
         <v>1</v>
@@ -1871,7 +1884,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:14">
@@ -1897,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K22" s="1">
         <v>1</v>
@@ -1909,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:14">
@@ -1935,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K23" s="1">
         <v>1</v>
@@ -1947,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:14">
@@ -1973,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K24" s="1">
         <v>1</v>
@@ -1985,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:14">
@@ -2005,13 +2018,13 @@
         <v>3</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K25" s="1">
         <v>1</v>
@@ -2023,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:14">
@@ -2043,13 +2056,13 @@
         <v>3</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K26" s="1">
         <v>1</v>
@@ -2061,7 +2074,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:14">
@@ -2081,13 +2094,13 @@
         <v>3</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K27" s="1">
         <v>1</v>
@@ -2099,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:14">
@@ -2119,25 +2132,25 @@
         <v>3</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1">
+        <v>20</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="3">
+        <v>100</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="K28" s="1">
-        <v>1</v>
-      </c>
-      <c r="L28" s="3">
-        <v>100</v>
-      </c>
-      <c r="M28" s="1">
-        <v>0</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:14">
@@ -2157,13 +2170,13 @@
         <v>20</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K29" s="1">
         <v>2</v>
@@ -2175,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:14">
@@ -2195,13 +2208,13 @@
         <v>10</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K30" s="1">
         <v>2</v>
@@ -2213,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:14">
@@ -2233,13 +2246,13 @@
         <v>5</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K31" s="1">
         <v>2</v>
@@ -2251,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:14">
@@ -2271,13 +2284,13 @@
         <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K32" s="1">
         <v>2</v>
@@ -2289,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:14">
@@ -2309,13 +2322,13 @@
         <v>8</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K33" s="1">
         <v>2</v>
@@ -2327,7 +2340,7 @@
         <v>2</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:14">
@@ -2347,13 +2360,13 @@
         <v>8</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K34" s="1">
         <v>2</v>
@@ -2365,7 +2378,7 @@
         <v>3</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:14">
@@ -2385,13 +2398,13 @@
         <v>8</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
@@ -2403,7 +2416,7 @@
         <v>1</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:14">
@@ -2423,13 +2436,13 @@
         <v>8</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K36" s="1">
         <v>1</v>
@@ -2441,7 +2454,7 @@
         <v>2</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" spans="3:14">
@@ -2461,13 +2474,13 @@
         <v>8</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K37" s="1">
         <v>1</v>
@@ -2479,7 +2492,7 @@
         <v>3</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:14">
@@ -2498,20 +2511,20 @@
         <v>1</v>
       </c>
       <c r="F39" s="1">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="G39" s="1">
         <v>5000</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I39" s="1">
+        <v>21</v>
+      </c>
+      <c r="J39" s="1">
         <v>50</v>
       </c>
-      <c r="J39" s="1">
-        <v>90</v>
-      </c>
       <c r="K39" s="1">
         <v>2</v>
       </c>
@@ -2522,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:14">
@@ -2536,20 +2549,20 @@
         <v>2</v>
       </c>
       <c r="F40" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G40" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I40" s="1">
+        <v>21</v>
+      </c>
+      <c r="J40" s="1">
         <v>50</v>
       </c>
-      <c r="J40" s="1">
-        <v>90</v>
-      </c>
       <c r="K40" s="1">
         <v>2</v>
       </c>
@@ -2560,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:14">
@@ -2574,20 +2587,20 @@
         <v>3</v>
       </c>
       <c r="F41" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G41" s="1">
         <v>1000</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I41" s="1">
+        <v>21</v>
+      </c>
+      <c r="J41" s="1">
         <v>50</v>
       </c>
-      <c r="J41" s="1">
-        <v>90</v>
-      </c>
       <c r="K41" s="1">
         <v>2</v>
       </c>
@@ -2598,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:14">
@@ -2612,7 +2625,7 @@
         <v>21</v>
       </c>
       <c r="F42" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="1">
         <v>5</v>
@@ -2621,11 +2634,11 @@
         <v>9</v>
       </c>
       <c r="I42" s="1">
+        <v>21</v>
+      </c>
+      <c r="J42" s="1">
         <v>50</v>
       </c>
-      <c r="J42" s="1">
-        <v>90</v>
-      </c>
       <c r="K42" s="1">
         <v>1</v>
       </c>
@@ -2636,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:14">
@@ -2650,7 +2663,7 @@
         <v>22</v>
       </c>
       <c r="F43" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G43" s="1">
         <v>40</v>
@@ -2659,11 +2672,11 @@
         <v>10</v>
       </c>
       <c r="I43" s="1">
+        <v>21</v>
+      </c>
+      <c r="J43" s="1">
         <v>50</v>
       </c>
-      <c r="J43" s="1">
-        <v>90</v>
-      </c>
       <c r="K43" s="1">
         <v>1</v>
       </c>
@@ -2674,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:14">
@@ -2688,7 +2701,7 @@
         <v>27</v>
       </c>
       <c r="F44" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" s="1">
         <v>10</v>
@@ -2697,11 +2710,11 @@
         <v>7</v>
       </c>
       <c r="I44" s="1">
+        <v>21</v>
+      </c>
+      <c r="J44" s="1">
         <v>50</v>
       </c>
-      <c r="J44" s="1">
-        <v>90</v>
-      </c>
       <c r="K44" s="1">
         <v>1</v>
       </c>
@@ -2712,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:14">
@@ -2726,7 +2739,7 @@
         <v>28</v>
       </c>
       <c r="F45" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="1">
         <v>5</v>
@@ -2735,11 +2748,11 @@
         <v>5</v>
       </c>
       <c r="I45" s="1">
+        <v>21</v>
+      </c>
+      <c r="J45" s="1">
         <v>50</v>
       </c>
-      <c r="J45" s="1">
-        <v>90</v>
-      </c>
       <c r="K45" s="1">
         <v>1</v>
       </c>
@@ -2750,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:14">
@@ -2764,20 +2777,20 @@
         <v>81</v>
       </c>
       <c r="F46" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="1">
         <v>5</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I46" s="1">
+        <v>21</v>
+      </c>
+      <c r="J46" s="1">
         <v>50</v>
       </c>
-      <c r="J46" s="1">
-        <v>90</v>
-      </c>
       <c r="K46" s="1">
         <v>1</v>
       </c>
@@ -2788,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:14">
@@ -2802,20 +2815,20 @@
         <v>82</v>
       </c>
       <c r="F47" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" s="1">
         <v>5</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I47" s="1">
+        <v>21</v>
+      </c>
+      <c r="J47" s="1">
         <v>50</v>
       </c>
-      <c r="J47" s="1">
-        <v>90</v>
-      </c>
       <c r="K47" s="1">
         <v>1</v>
       </c>
@@ -2826,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:14">
@@ -2840,20 +2853,20 @@
         <v>83</v>
       </c>
       <c r="F48" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="1">
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I48" s="1">
+        <v>21</v>
+      </c>
+      <c r="J48" s="1">
         <v>50</v>
       </c>
-      <c r="J48" s="1">
-        <v>90</v>
-      </c>
       <c r="K48" s="1">
         <v>1</v>
       </c>
@@ -2864,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:14">
@@ -2878,20 +2891,20 @@
         <v>84</v>
       </c>
       <c r="F49" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" s="1">
         <v>5</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I49" s="1">
+        <v>21</v>
+      </c>
+      <c r="J49" s="1">
         <v>50</v>
       </c>
-      <c r="J49" s="1">
-        <v>90</v>
-      </c>
       <c r="K49" s="1">
         <v>1</v>
       </c>
@@ -2902,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:14">
@@ -2916,20 +2929,20 @@
         <v>1001</v>
       </c>
       <c r="F50" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G50" s="1">
         <v>40</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I50" s="1">
+        <v>21</v>
+      </c>
+      <c r="J50" s="1">
         <v>50</v>
       </c>
-      <c r="J50" s="1">
-        <v>90</v>
-      </c>
       <c r="K50" s="1">
         <v>2</v>
       </c>
@@ -2940,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:14">
@@ -2954,20 +2967,20 @@
         <v>1002</v>
       </c>
       <c r="F51" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G51" s="1">
         <v>20</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I51" s="1">
+        <v>21</v>
+      </c>
+      <c r="J51" s="1">
         <v>50</v>
       </c>
-      <c r="J51" s="1">
-        <v>90</v>
-      </c>
       <c r="K51" s="1">
         <v>2</v>
       </c>
@@ -2978,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:14">
@@ -2992,20 +3005,20 @@
         <v>1003</v>
       </c>
       <c r="F52" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" s="1">
         <v>10</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I52" s="1">
+        <v>21</v>
+      </c>
+      <c r="J52" s="1">
         <v>50</v>
       </c>
-      <c r="J52" s="1">
-        <v>90</v>
-      </c>
       <c r="K52" s="1">
         <v>2</v>
       </c>
@@ -3016,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:14">
@@ -3030,20 +3043,20 @@
         <v>1004</v>
       </c>
       <c r="F53" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G53" s="1">
         <v>15</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I53" s="1">
+        <v>21</v>
+      </c>
+      <c r="J53" s="1">
         <v>50</v>
       </c>
-      <c r="J53" s="1">
-        <v>90</v>
-      </c>
       <c r="K53" s="1">
         <v>2</v>
       </c>
@@ -3054,7 +3067,7 @@
         <v>1</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:14">
@@ -3068,20 +3081,20 @@
         <v>1005</v>
       </c>
       <c r="F54" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54" s="1">
         <v>15</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I54" s="1">
+        <v>21</v>
+      </c>
+      <c r="J54" s="1">
         <v>50</v>
       </c>
-      <c r="J54" s="1">
-        <v>90</v>
-      </c>
       <c r="K54" s="1">
         <v>2</v>
       </c>
@@ -3092,7 +3105,7 @@
         <v>2</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:14">
@@ -3106,19 +3119,19 @@
         <v>1006</v>
       </c>
       <c r="F55" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55" s="1">
         <v>15</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I55" s="1">
+        <v>21</v>
+      </c>
+      <c r="J55" s="1">
         <v>50</v>
-      </c>
-      <c r="J55" s="1">
-        <v>90</v>
       </c>
       <c r="K55" s="1">
         <v>2</v>
@@ -3130,7 +3143,7 @@
         <v>3</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:14">
@@ -3144,20 +3157,20 @@
         <v>1007</v>
       </c>
       <c r="F56" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56" s="1">
         <v>15</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I56" s="1">
+        <v>21</v>
+      </c>
+      <c r="J56" s="1">
         <v>50</v>
       </c>
-      <c r="J56" s="1">
-        <v>90</v>
-      </c>
       <c r="K56" s="1">
         <v>1</v>
       </c>
@@ -3168,7 +3181,7 @@
         <v>1</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:14">
@@ -3182,20 +3195,20 @@
         <v>1008</v>
       </c>
       <c r="F57" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G57" s="1">
         <v>15</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I57" s="1">
+        <v>21</v>
+      </c>
+      <c r="J57" s="1">
         <v>50</v>
       </c>
-      <c r="J57" s="1">
-        <v>90</v>
-      </c>
       <c r="K57" s="1">
         <v>1</v>
       </c>
@@ -3206,7 +3219,7 @@
         <v>2</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:14">
@@ -3220,19 +3233,19 @@
         <v>1009</v>
       </c>
       <c r="F58" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58" s="1">
         <v>15</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I58" s="1">
+        <v>21</v>
+      </c>
+      <c r="J58" s="1">
         <v>50</v>
-      </c>
-      <c r="J58" s="1">
-        <v>90</v>
       </c>
       <c r="K58" s="1">
         <v>1</v>
@@ -3244,7 +3257,7 @@
         <v>3</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
+    <sheet name="技能" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,8 +60,41 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+ID* 10 + level
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="72">
   <si>
     <t>#</t>
   </si>
@@ -146,70 +180,136 @@
     <t>移速</t>
   </si>
   <si>
+    <t>冷却</t>
+  </si>
+  <si>
     <t>1,2,3,4,5,7,9,10</t>
   </si>
   <si>
+    <t>生命</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>暴击率</t>
+  </si>
+  <si>
+    <t>爆伤加成</t>
+  </si>
+  <si>
+    <t>伤害加成</t>
+  </si>
+  <si>
+    <t>伤害减免</t>
+  </si>
+  <si>
+    <t>金币加成</t>
+  </si>
+  <si>
+    <t>经验加成</t>
+  </si>
+  <si>
+    <t>品质加成</t>
+  </si>
+  <si>
+    <t>爆率加成</t>
+  </si>
+  <si>
+    <t>生命加成</t>
+  </si>
+  <si>
+    <t>防御加成</t>
+  </si>
+  <si>
+    <t>攻击加成</t>
+  </si>
+  <si>
+    <t>物攻加成</t>
+  </si>
+  <si>
+    <t>魔法加成</t>
+  </si>
+  <si>
+    <t>道术加成</t>
+  </si>
+  <si>
+    <t>物伤加成</t>
+  </si>
+  <si>
+    <t>魔伤加成</t>
+  </si>
+  <si>
+    <t>道伤加成</t>
+  </si>
+  <si>
     <t>全技能等级增加</t>
   </si>
   <si>
-    <t>生命</t>
-  </si>
-  <si>
-    <t>防御</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>暴击率</t>
-  </si>
-  <si>
-    <t>爆伤加成</t>
-  </si>
-  <si>
-    <t>伤害加成</t>
-  </si>
-  <si>
-    <t>伤害减免</t>
-  </si>
-  <si>
-    <t>金币加成</t>
-  </si>
-  <si>
-    <t>经验加成</t>
-  </si>
-  <si>
-    <t>品质加成</t>
-  </si>
-  <si>
-    <t>爆率加成</t>
-  </si>
-  <si>
-    <t>生命加成</t>
-  </si>
-  <si>
-    <t>防御加成</t>
-  </si>
-  <si>
-    <t>攻击加成</t>
-  </si>
-  <si>
-    <t>物攻加成</t>
-  </si>
-  <si>
-    <t>魔法加成</t>
-  </si>
-  <si>
-    <t>道术加成</t>
-  </si>
-  <si>
-    <t>物伤加成</t>
-  </si>
-  <si>
-    <t>魔伤加成</t>
-  </si>
-  <si>
-    <t>道伤加成</t>
+    <t>战士技能1等级</t>
+  </si>
+  <si>
+    <t>战士技能2等级</t>
+  </si>
+  <si>
+    <t>战士技能3等级</t>
+  </si>
+  <si>
+    <t>战士技能4等级</t>
+  </si>
+  <si>
+    <t>战士技能5等级</t>
+  </si>
+  <si>
+    <t>战士技能6等级</t>
+  </si>
+  <si>
+    <t>战士技能7等级</t>
+  </si>
+  <si>
+    <t>法师技能1等级</t>
+  </si>
+  <si>
+    <t>法师技能2等级</t>
+  </si>
+  <si>
+    <t>法师技能3等级</t>
+  </si>
+  <si>
+    <t>法师技能4等级</t>
+  </si>
+  <si>
+    <t>法师技能5等级</t>
+  </si>
+  <si>
+    <t>法师技能6等级</t>
+  </si>
+  <si>
+    <t>法师技能7等级</t>
+  </si>
+  <si>
+    <t>道士技能1等级</t>
+  </si>
+  <si>
+    <t>道士技能2等级</t>
+  </si>
+  <si>
+    <t>道士技能3等级</t>
+  </si>
+  <si>
+    <t>道士技能4等级</t>
+  </si>
+  <si>
+    <t>道士技能5等级</t>
+  </si>
+  <si>
+    <t>道士技能6等级</t>
+  </si>
+  <si>
+    <t>道士技能7等级</t>
   </si>
 </sst>
 </file>
@@ -388,12 +488,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1346,7 +1446,7 @@
         <v>2</v>
       </c>
       <c r="L6" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -1384,7 +1484,7 @@
         <v>2</v>
       </c>
       <c r="L7" s="1">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
@@ -1422,7 +1522,7 @@
         <v>2</v>
       </c>
       <c r="L8" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
@@ -1460,7 +1560,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
@@ -1498,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
@@ -1536,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="1">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
@@ -1650,7 +1750,7 @@
         <v>2</v>
       </c>
       <c r="L14" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
@@ -1705,16 +1805,16 @@
         <v>1</v>
       </c>
       <c r="E16" s="1">
-        <v>222</v>
+        <v>10</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>28</v>
+        <v>3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>7</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -1726,13 +1826,13 @@
         <v>1</v>
       </c>
       <c r="L16" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:14">
@@ -1752,7 +1852,7 @@
         <v>1000</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
@@ -1790,7 +1890,7 @@
         <v>100</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
@@ -1828,7 +1928,7 @@
         <v>100</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
@@ -2018,7 +2118,7 @@
         <v>3</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
@@ -2056,7 +2156,7 @@
         <v>3</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
@@ -2094,7 +2194,7 @@
         <v>3</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
@@ -2132,7 +2232,7 @@
         <v>3</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
@@ -2170,7 +2270,7 @@
         <v>20</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
@@ -2208,7 +2308,7 @@
         <v>10</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
@@ -2246,7 +2346,7 @@
         <v>5</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
@@ -2284,7 +2384,7 @@
         <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
@@ -2322,7 +2422,7 @@
         <v>8</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
@@ -2360,7 +2460,7 @@
         <v>8</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
@@ -2398,7 +2498,7 @@
         <v>8</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
@@ -2436,7 +2536,7 @@
         <v>8</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
@@ -2474,7 +2574,7 @@
         <v>8</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
@@ -2517,7 +2617,7 @@
         <v>5000</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I39" s="1">
         <v>21</v>
@@ -2555,7 +2655,7 @@
         <v>1000</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I40" s="1">
         <v>21</v>
@@ -2593,7 +2693,7 @@
         <v>1000</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I41" s="1">
         <v>21</v>
@@ -2783,7 +2883,7 @@
         <v>5</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I46" s="1">
         <v>21</v>
@@ -2821,7 +2921,7 @@
         <v>5</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I47" s="1">
         <v>21</v>
@@ -2859,7 +2959,7 @@
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I48" s="1">
         <v>21</v>
@@ -2897,7 +2997,7 @@
         <v>5</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I49" s="1">
         <v>21</v>
@@ -2935,7 +3035,7 @@
         <v>40</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I50" s="1">
         <v>21</v>
@@ -2973,7 +3073,7 @@
         <v>20</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I51" s="1">
         <v>21</v>
@@ -3011,7 +3111,7 @@
         <v>10</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I52" s="1">
         <v>21</v>
@@ -3049,7 +3149,7 @@
         <v>15</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I53" s="1">
         <v>21</v>
@@ -3087,7 +3187,7 @@
         <v>15</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I54" s="1">
         <v>21</v>
@@ -3125,7 +3225,7 @@
         <v>15</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I55" s="1">
         <v>21</v>
@@ -3163,7 +3263,7 @@
         <v>15</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I56" s="1">
         <v>21</v>
@@ -3201,7 +3301,7 @@
         <v>15</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I57" s="1">
         <v>21</v>
@@ -3239,7 +3339,7 @@
         <v>15</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I58" s="1">
         <v>21</v>
@@ -3271,4 +3371,986 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C1:N27"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <cols>
+    <col min="8" max="8" width="13.9166666666667" customWidth="1"/>
+    <col min="14" max="14" width="14.5833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="C6" s="1">
+        <v>10001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>21000</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="C7" s="1">
+        <v>10002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>21001</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>10</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="C8" s="1">
+        <v>10003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>21002</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>10</v>
+      </c>
+      <c r="M8" s="1">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="C9" s="1">
+        <v>10004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>21003</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <v>10</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="C10" s="1">
+        <v>10005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>21004</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>10</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="C11" s="1">
+        <v>10006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>21005</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>10</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="C12" s="1">
+        <v>10007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>21006</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>10</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="C13" s="1">
+        <v>10008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>21007</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>10</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="C14" s="1">
+        <v>10009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>22001</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>10</v>
+      </c>
+      <c r="M14" s="1">
+        <v>2</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="C15" s="1">
+        <v>10010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>22002</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>10</v>
+      </c>
+      <c r="M15" s="1">
+        <v>2</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="3:14">
+      <c r="C16" s="1">
+        <v>10011</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>22003</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
+        <v>10</v>
+      </c>
+      <c r="M16" s="1">
+        <v>2</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14">
+      <c r="C17" s="1">
+        <v>10012</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>22004</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>10</v>
+      </c>
+      <c r="M17" s="1">
+        <v>2</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14">
+      <c r="C18" s="1">
+        <v>10013</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>22005</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <v>10</v>
+      </c>
+      <c r="M18" s="1">
+        <v>2</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14">
+      <c r="C19" s="1">
+        <v>10014</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>22006</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
+        <v>10</v>
+      </c>
+      <c r="M19" s="1">
+        <v>2</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="3:14">
+      <c r="C20" s="1">
+        <v>10015</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>22007</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>10</v>
+      </c>
+      <c r="M20" s="1">
+        <v>2</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14">
+      <c r="C21" s="1">
+        <v>10016</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>23001</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1">
+        <v>10</v>
+      </c>
+      <c r="M21" s="1">
+        <v>3</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14">
+      <c r="C22" s="1">
+        <v>10017</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>23002</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>10</v>
+      </c>
+      <c r="M22" s="1">
+        <v>3</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14">
+      <c r="C23" s="1">
+        <v>10018</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>23003</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1">
+        <v>10</v>
+      </c>
+      <c r="M23" s="1">
+        <v>3</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14">
+      <c r="C24" s="1">
+        <v>10019</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>23004</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
+        <v>10</v>
+      </c>
+      <c r="M24" s="1">
+        <v>3</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14">
+      <c r="C25" s="1">
+        <v>10020</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>23005</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
+        <v>10</v>
+      </c>
+      <c r="M25" s="1">
+        <v>3</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14">
+      <c r="C26" s="1">
+        <v>10021</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>23006</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1">
+        <v>10</v>
+      </c>
+      <c r="M26" s="1">
+        <v>3</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14">
+      <c r="C27" s="1">
+        <v>10022</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>23007</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>99999</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <v>10</v>
+      </c>
+      <c r="M27" s="1">
+        <v>3</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 E3:E5 N3:N5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
+    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="C3" authorId="0">
@@ -56,6 +57,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="M3" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 均匀随机
+2 线性增伤随机
+3 指数增伤随机</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -64,6 +89,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
+    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="C3" authorId="0">
@@ -89,12 +115,60 @@
         </r>
       </text>
     </comment>
+    <comment ref="M3" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 均匀随机
+2 线性增伤随机
+3 指数增伤随机</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M4" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 均匀随机
+2 线性增伤随机
+3 指数增伤随机</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="73">
   <si>
     <t>#</t>
   </si>
@@ -127,6 +201,9 @@
   </si>
   <si>
     <t>Rate</t>
+  </si>
+  <si>
+    <t>RateType</t>
   </si>
   <si>
     <t>Role</t>
@@ -488,12 +565,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1280,7 +1357,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N58"/>
+  <dimension ref="C1:O58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1288,22 +1365,22 @@
     <col min="5" max="5" width="9" style="1"/>
     <col min="6" max="7" width="13" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.1666666666667" style="1" customWidth="1"/>
-    <col min="9" max="13" width="13" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.625" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="1"/>
+    <col min="9" max="14" width="13" style="1" customWidth="1"/>
+    <col min="15" max="15" width="19.625" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:14">
-      <c r="N1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:14">
-      <c r="N2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="3:14">
+    <row r="1" customHeight="1" spans="3:15">
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:15">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="3:15">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1340,10 +1417,13 @@
       <c r="N3" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:14">
+      <c r="O3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="3:15">
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -1376,48 +1456,54 @@
         <v>11</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="3:14">
+        <v>12</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="3:15">
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:14">
+        <v>16</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:15">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1434,7 +1520,7 @@
         <v>3</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -1449,13 +1535,16 @@
         <v>10</v>
       </c>
       <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:15">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1472,7 +1561,7 @@
         <v>3</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
@@ -1487,13 +1576,16 @@
         <v>5</v>
       </c>
       <c r="M7" s="1">
-        <v>0</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:15">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1510,7 +1602,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -1525,13 +1617,16 @@
         <v>10</v>
       </c>
       <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:15">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1548,7 +1643,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
@@ -1563,13 +1658,16 @@
         <v>5</v>
       </c>
       <c r="M9" s="1">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:15">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1601,13 +1699,16 @@
         <v>5</v>
       </c>
       <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:15">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1639,13 +1740,16 @@
         <v>5</v>
       </c>
       <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:15">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1677,13 +1781,16 @@
         <v>30</v>
       </c>
       <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:14">
+        <v>2</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:15">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1715,13 +1822,16 @@
         <v>30</v>
       </c>
       <c r="M13" s="1">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:14">
+        <v>2</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:15">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1753,13 +1863,16 @@
         <v>20</v>
       </c>
       <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:14">
+        <v>2</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:15">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1791,13 +1904,16 @@
         <v>30</v>
       </c>
       <c r="M15" s="1">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:14">
+        <v>2</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:15">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1829,13 +1945,16 @@
         <v>20</v>
       </c>
       <c r="M16" s="1">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:14">
+        <v>2</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:15">
       <c r="C18" s="1">
         <v>101</v>
       </c>
@@ -1852,7 +1971,7 @@
         <v>1000</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
@@ -1867,13 +1986,16 @@
         <v>100</v>
       </c>
       <c r="M18" s="1">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:15">
       <c r="C19" s="1">
         <v>102</v>
       </c>
@@ -1890,7 +2012,7 @@
         <v>100</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
@@ -1905,13 +2027,16 @@
         <v>100</v>
       </c>
       <c r="M19" s="1">
-        <v>0</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:15">
       <c r="C20" s="1">
         <v>103</v>
       </c>
@@ -1928,7 +2053,7 @@
         <v>100</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
@@ -1943,13 +2068,16 @@
         <v>100</v>
       </c>
       <c r="M20" s="1">
-        <v>0</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:15">
       <c r="C21" s="1">
         <v>104</v>
       </c>
@@ -1981,13 +2109,16 @@
         <v>100</v>
       </c>
       <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:15">
       <c r="C22" s="1">
         <v>105</v>
       </c>
@@ -2019,13 +2150,16 @@
         <v>100</v>
       </c>
       <c r="M22" s="1">
-        <v>0</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:15">
       <c r="C23" s="1">
         <v>106</v>
       </c>
@@ -2057,13 +2191,16 @@
         <v>100</v>
       </c>
       <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:15">
       <c r="C24" s="1">
         <v>107</v>
       </c>
@@ -2095,13 +2232,16 @@
         <v>100</v>
       </c>
       <c r="M24" s="1">
-        <v>0</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:15">
       <c r="C25" s="1">
         <v>108</v>
       </c>
@@ -2118,7 +2258,7 @@
         <v>3</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
@@ -2133,13 +2273,16 @@
         <v>100</v>
       </c>
       <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:14">
+        <v>2</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:15">
       <c r="C26" s="1">
         <v>109</v>
       </c>
@@ -2156,7 +2299,7 @@
         <v>3</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
@@ -2171,13 +2314,16 @@
         <v>100</v>
       </c>
       <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:14">
+        <v>2</v>
+      </c>
+      <c r="N26" s="1">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:15">
       <c r="C27" s="1">
         <v>110</v>
       </c>
@@ -2194,7 +2340,7 @@
         <v>3</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
@@ -2209,13 +2355,16 @@
         <v>100</v>
       </c>
       <c r="M27" s="1">
-        <v>0</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:14">
+        <v>2</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:15">
       <c r="C28" s="1">
         <v>111</v>
       </c>
@@ -2232,7 +2381,7 @@
         <v>3</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
@@ -2247,13 +2396,16 @@
         <v>100</v>
       </c>
       <c r="M28" s="1">
-        <v>0</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:14">
+        <v>2</v>
+      </c>
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:15">
       <c r="C29" s="1">
         <v>112</v>
       </c>
@@ -2270,7 +2422,7 @@
         <v>20</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
@@ -2285,13 +2437,16 @@
         <v>100</v>
       </c>
       <c r="M29" s="1">
-        <v>0</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:15">
       <c r="C30" s="1">
         <v>113</v>
       </c>
@@ -2308,7 +2463,7 @@
         <v>10</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
@@ -2323,13 +2478,16 @@
         <v>100</v>
       </c>
       <c r="M30" s="1">
-        <v>0</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N30" s="1">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:15">
       <c r="C31" s="1">
         <v>114</v>
       </c>
@@ -2346,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
@@ -2361,13 +2519,16 @@
         <v>100</v>
       </c>
       <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:15">
       <c r="C32" s="1">
         <v>115</v>
       </c>
@@ -2384,7 +2545,7 @@
         <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
@@ -2401,11 +2562,14 @@
       <c r="M32" s="1">
         <v>1</v>
       </c>
-      <c r="N32" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:14">
+      <c r="N32" s="1">
+        <v>1</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:15">
       <c r="C33" s="1">
         <v>116</v>
       </c>
@@ -2422,7 +2586,7 @@
         <v>8</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
@@ -2437,13 +2601,16 @@
         <v>100</v>
       </c>
       <c r="M33" s="1">
-        <v>2</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N33" s="1">
+        <v>2</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:15">
       <c r="C34" s="1">
         <v>117</v>
       </c>
@@ -2460,7 +2627,7 @@
         <v>8</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
@@ -2475,13 +2642,16 @@
         <v>100</v>
       </c>
       <c r="M34" s="1">
-        <v>3</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N34" s="1">
+        <v>3</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:15">
       <c r="C35" s="1">
         <v>118</v>
       </c>
@@ -2498,7 +2668,7 @@
         <v>8</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
@@ -2515,11 +2685,14 @@
       <c r="M35" s="1">
         <v>1</v>
       </c>
-      <c r="N35" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:14">
+      <c r="N35" s="1">
+        <v>1</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:15">
       <c r="C36" s="1">
         <v>119</v>
       </c>
@@ -2536,7 +2709,7 @@
         <v>8</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
@@ -2551,13 +2724,16 @@
         <v>100</v>
       </c>
       <c r="M36" s="1">
-        <v>2</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N36" s="1">
+        <v>2</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="3:15">
       <c r="C37" s="1">
         <v>120</v>
       </c>
@@ -2574,7 +2750,7 @@
         <v>8</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
@@ -2589,18 +2765,22 @@
         <v>100</v>
       </c>
       <c r="M37" s="1">
-        <v>3</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N37" s="1">
+        <v>3</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:15">
       <c r="H38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
-    </row>
-    <row r="39" customHeight="1" spans="3:14">
+      <c r="M38" s="3"/>
+    </row>
+    <row r="39" customHeight="1" spans="3:15">
       <c r="C39" s="1">
         <v>201</v>
       </c>
@@ -2617,7 +2797,7 @@
         <v>5000</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I39" s="1">
         <v>21</v>
@@ -2632,13 +2812,16 @@
         <v>100</v>
       </c>
       <c r="M39" s="1">
-        <v>0</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N39" s="1">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:15">
       <c r="C40" s="1">
         <v>202</v>
       </c>
@@ -2655,7 +2838,7 @@
         <v>1000</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I40" s="1">
         <v>21</v>
@@ -2670,13 +2853,16 @@
         <v>100</v>
       </c>
       <c r="M40" s="1">
-        <v>0</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N40" s="1">
+        <v>0</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:15">
       <c r="C41" s="1">
         <v>203</v>
       </c>
@@ -2693,7 +2879,7 @@
         <v>1000</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I41" s="1">
         <v>21</v>
@@ -2708,13 +2894,16 @@
         <v>100</v>
       </c>
       <c r="M41" s="1">
-        <v>0</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N41" s="1">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:15">
       <c r="C42" s="1">
         <v>204</v>
       </c>
@@ -2746,13 +2935,16 @@
         <v>100</v>
       </c>
       <c r="M42" s="1">
-        <v>0</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N42" s="1">
+        <v>0</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:15">
       <c r="C43" s="1">
         <v>205</v>
       </c>
@@ -2784,13 +2976,16 @@
         <v>100</v>
       </c>
       <c r="M43" s="1">
-        <v>0</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N43" s="1">
+        <v>0</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:15">
       <c r="C44" s="1">
         <v>206</v>
       </c>
@@ -2822,13 +3017,16 @@
         <v>100</v>
       </c>
       <c r="M44" s="1">
-        <v>0</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N44" s="1">
+        <v>0</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:15">
       <c r="C45" s="1">
         <v>207</v>
       </c>
@@ -2860,13 +3058,16 @@
         <v>100</v>
       </c>
       <c r="M45" s="1">
-        <v>0</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N45" s="1">
+        <v>0</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:15">
       <c r="C46" s="1">
         <v>208</v>
       </c>
@@ -2883,7 +3084,7 @@
         <v>5</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I46" s="1">
         <v>21</v>
@@ -2898,13 +3099,16 @@
         <v>100</v>
       </c>
       <c r="M46" s="1">
-        <v>0</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:14">
+        <v>2</v>
+      </c>
+      <c r="N46" s="1">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:15">
       <c r="C47" s="1">
         <v>209</v>
       </c>
@@ -2921,7 +3125,7 @@
         <v>5</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I47" s="1">
         <v>21</v>
@@ -2936,13 +3140,16 @@
         <v>100</v>
       </c>
       <c r="M47" s="1">
-        <v>0</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:14">
+        <v>2</v>
+      </c>
+      <c r="N47" s="1">
+        <v>0</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:15">
       <c r="C48" s="1">
         <v>210</v>
       </c>
@@ -2959,7 +3166,7 @@
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I48" s="1">
         <v>21</v>
@@ -2974,13 +3181,16 @@
         <v>100</v>
       </c>
       <c r="M48" s="1">
-        <v>0</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:14">
+        <v>2</v>
+      </c>
+      <c r="N48" s="1">
+        <v>0</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:15">
       <c r="C49" s="1">
         <v>211</v>
       </c>
@@ -2997,7 +3207,7 @@
         <v>5</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I49" s="1">
         <v>21</v>
@@ -3012,13 +3222,16 @@
         <v>100</v>
       </c>
       <c r="M49" s="1">
-        <v>0</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:14">
+        <v>2</v>
+      </c>
+      <c r="N49" s="1">
+        <v>0</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:15">
       <c r="C50" s="1">
         <v>212</v>
       </c>
@@ -3035,7 +3248,7 @@
         <v>40</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I50" s="1">
         <v>21</v>
@@ -3050,13 +3263,16 @@
         <v>100</v>
       </c>
       <c r="M50" s="1">
-        <v>0</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N50" s="1">
+        <v>0</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:15">
       <c r="C51" s="1">
         <v>213</v>
       </c>
@@ -3073,7 +3289,7 @@
         <v>20</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I51" s="1">
         <v>21</v>
@@ -3088,13 +3304,16 @@
         <v>100</v>
       </c>
       <c r="M51" s="1">
-        <v>0</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N51" s="1">
+        <v>0</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:15">
       <c r="C52" s="1">
         <v>214</v>
       </c>
@@ -3111,7 +3330,7 @@
         <v>10</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I52" s="1">
         <v>21</v>
@@ -3126,13 +3345,16 @@
         <v>100</v>
       </c>
       <c r="M52" s="1">
-        <v>0</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N52" s="1">
+        <v>0</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:15">
       <c r="C53" s="1">
         <v>215</v>
       </c>
@@ -3149,7 +3371,7 @@
         <v>15</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I53" s="1">
         <v>21</v>
@@ -3166,11 +3388,14 @@
       <c r="M53" s="1">
         <v>1</v>
       </c>
-      <c r="N53" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:14">
+      <c r="N53" s="1">
+        <v>1</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:15">
       <c r="C54" s="1">
         <v>216</v>
       </c>
@@ -3187,7 +3412,7 @@
         <v>15</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I54" s="1">
         <v>21</v>
@@ -3202,13 +3427,16 @@
         <v>100</v>
       </c>
       <c r="M54" s="1">
-        <v>2</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N54" s="1">
+        <v>2</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:15">
       <c r="C55" s="1">
         <v>217</v>
       </c>
@@ -3225,7 +3453,7 @@
         <v>15</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I55" s="1">
         <v>21</v>
@@ -3240,13 +3468,16 @@
         <v>100</v>
       </c>
       <c r="M55" s="1">
-        <v>3</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N55" s="1">
+        <v>3</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:15">
       <c r="C56" s="1">
         <v>218</v>
       </c>
@@ -3263,7 +3494,7 @@
         <v>15</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I56" s="1">
         <v>21</v>
@@ -3280,11 +3511,14 @@
       <c r="M56" s="1">
         <v>1</v>
       </c>
-      <c r="N56" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:14">
+      <c r="N56" s="1">
+        <v>1</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:15">
       <c r="C57" s="1">
         <v>219</v>
       </c>
@@ -3301,7 +3535,7 @@
         <v>15</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I57" s="1">
         <v>21</v>
@@ -3316,13 +3550,16 @@
         <v>100</v>
       </c>
       <c r="M57" s="1">
-        <v>2</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N57" s="1">
+        <v>2</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:15">
       <c r="C58" s="1">
         <v>220</v>
       </c>
@@ -3339,7 +3576,7 @@
         <v>15</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I58" s="1">
         <v>21</v>
@@ -3354,15 +3591,18 @@
         <v>100</v>
       </c>
       <c r="M58" s="1">
-        <v>3</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="N58" s="1">
+        <v>3</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 E3:E5 N3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 E3:E5 O3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -3376,24 +3616,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N27"/>
+  <dimension ref="C1:O27"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
     <col min="8" max="8" width="13.9166666666667" customWidth="1"/>
-    <col min="14" max="14" width="14.5833333333333" customWidth="1"/>
+    <col min="15" max="15" width="14.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
-      <c r="N1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
-      <c r="N2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+    <row r="1" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -3430,10 +3670,13 @@
       <c r="N3" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+      <c r="O3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -3466,48 +3709,54 @@
         <v>11</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+        <v>12</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+        <v>16</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
       <c r="C6" s="1">
         <v>10001</v>
       </c>
@@ -3524,7 +3773,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -3539,13 +3788,16 @@
         <v>1</v>
       </c>
       <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
       <c r="C7" s="1">
         <v>10002</v>
       </c>
@@ -3562,7 +3814,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
@@ -3577,13 +3829,16 @@
         <v>10</v>
       </c>
       <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
       <c r="C8" s="1">
         <v>10003</v>
       </c>
@@ -3600,7 +3855,7 @@
         <v>2</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -3615,13 +3870,16 @@
         <v>10</v>
       </c>
       <c r="M8" s="1">
-        <v>1</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N8" s="1">
+        <v>1</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
       <c r="C9" s="1">
         <v>10004</v>
       </c>
@@ -3638,7 +3896,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
@@ -3653,13 +3911,16 @@
         <v>10</v>
       </c>
       <c r="M9" s="1">
-        <v>1</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
       <c r="C10" s="1">
         <v>10005</v>
       </c>
@@ -3676,7 +3937,7 @@
         <v>2</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
@@ -3691,13 +3952,16 @@
         <v>10</v>
       </c>
       <c r="M10" s="1">
-        <v>1</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
       <c r="C11" s="1">
         <v>10006</v>
       </c>
@@ -3714,7 +3978,7 @@
         <v>2</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -3729,13 +3993,16 @@
         <v>10</v>
       </c>
       <c r="M11" s="1">
-        <v>1</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
       <c r="C12" s="1">
         <v>10007</v>
       </c>
@@ -3752,7 +4019,7 @@
         <v>2</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
@@ -3767,13 +4034,16 @@
         <v>10</v>
       </c>
       <c r="M12" s="1">
-        <v>1</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
       <c r="C13" s="1">
         <v>10008</v>
       </c>
@@ -3790,7 +4060,7 @@
         <v>2</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
@@ -3805,13 +4075,16 @@
         <v>10</v>
       </c>
       <c r="M13" s="1">
-        <v>1</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
       <c r="C14" s="1">
         <v>10009</v>
       </c>
@@ -3828,7 +4101,7 @@
         <v>2</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -3843,13 +4116,16 @@
         <v>10</v>
       </c>
       <c r="M14" s="1">
-        <v>2</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="16" customHeight="1" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N14" s="1">
+        <v>2</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="16" customHeight="1" spans="3:15">
       <c r="C15" s="1">
         <v>10010</v>
       </c>
@@ -3866,7 +4142,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
@@ -3881,13 +4157,16 @@
         <v>10</v>
       </c>
       <c r="M15" s="1">
-        <v>2</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N15" s="1">
+        <v>2</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="3:15">
       <c r="C16" s="1">
         <v>10011</v>
       </c>
@@ -3904,7 +4183,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -3919,13 +4198,16 @@
         <v>10</v>
       </c>
       <c r="M16" s="1">
-        <v>2</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N16" s="1">
+        <v>2</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="3:15">
       <c r="C17" s="1">
         <v>10012</v>
       </c>
@@ -3942,7 +4224,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -3957,13 +4239,16 @@
         <v>10</v>
       </c>
       <c r="M17" s="1">
-        <v>2</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N17" s="1">
+        <v>2</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15">
       <c r="C18" s="1">
         <v>10013</v>
       </c>
@@ -3980,7 +4265,7 @@
         <v>2</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
@@ -3995,13 +4280,16 @@
         <v>10</v>
       </c>
       <c r="M18" s="1">
-        <v>2</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N18" s="1">
+        <v>2</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15">
       <c r="C19" s="1">
         <v>10014</v>
       </c>
@@ -4018,7 +4306,7 @@
         <v>2</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
@@ -4033,13 +4321,16 @@
         <v>10</v>
       </c>
       <c r="M19" s="1">
-        <v>2</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N19" s="1">
+        <v>2</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="3:15">
       <c r="C20" s="1">
         <v>10015</v>
       </c>
@@ -4056,7 +4347,7 @@
         <v>2</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
@@ -4071,13 +4362,16 @@
         <v>10</v>
       </c>
       <c r="M20" s="1">
-        <v>2</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="3:14">
+        <v>3</v>
+      </c>
+      <c r="N20" s="1">
+        <v>2</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15">
       <c r="C21" s="1">
         <v>10016</v>
       </c>
@@ -4094,7 +4388,7 @@
         <v>2</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
@@ -4111,11 +4405,14 @@
       <c r="M21" s="1">
         <v>3</v>
       </c>
-      <c r="N21" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="3:14">
+      <c r="N21" s="1">
+        <v>3</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15">
       <c r="C22" s="1">
         <v>10017</v>
       </c>
@@ -4132,7 +4429,7 @@
         <v>2</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
@@ -4149,11 +4446,14 @@
       <c r="M22" s="1">
         <v>3</v>
       </c>
-      <c r="N22" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="3:14">
+      <c r="N22" s="1">
+        <v>3</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15">
       <c r="C23" s="1">
         <v>10018</v>
       </c>
@@ -4170,7 +4470,7 @@
         <v>2</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
@@ -4187,11 +4487,14 @@
       <c r="M23" s="1">
         <v>3</v>
       </c>
-      <c r="N23" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="3:14">
+      <c r="N23" s="1">
+        <v>3</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15">
       <c r="C24" s="1">
         <v>10019</v>
       </c>
@@ -4208,7 +4511,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
@@ -4225,11 +4528,14 @@
       <c r="M24" s="1">
         <v>3</v>
       </c>
-      <c r="N24" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="3:14">
+      <c r="N24" s="1">
+        <v>3</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15">
       <c r="C25" s="1">
         <v>10020</v>
       </c>
@@ -4246,7 +4552,7 @@
         <v>2</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
@@ -4263,11 +4569,14 @@
       <c r="M25" s="1">
         <v>3</v>
       </c>
-      <c r="N25" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="3:14">
+      <c r="N25" s="1">
+        <v>3</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15">
       <c r="C26" s="1">
         <v>10021</v>
       </c>
@@ -4284,7 +4593,7 @@
         <v>2</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
@@ -4301,11 +4610,14 @@
       <c r="M26" s="1">
         <v>3</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="3:14">
+      <c r="N26" s="1">
+        <v>3</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15">
       <c r="C27" s="1">
         <v>10022</v>
       </c>
@@ -4322,7 +4634,7 @@
         <v>2</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
@@ -4339,13 +4651,16 @@
       <c r="M27" s="1">
         <v>3</v>
       </c>
-      <c r="N27" s="1" t="s">
-        <v>71</v>
+      <c r="N27" s="1">
+        <v>3</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 E3:E5 N3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 E3:E5 O3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -1529,7 +1529,7 @@
         <v>99999</v>
       </c>
       <c r="K6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="1">
         <v>10</v>
@@ -1570,7 +1570,7 @@
         <v>99999</v>
       </c>
       <c r="K7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" s="1">
         <v>5</v>
@@ -1611,7 +1611,7 @@
         <v>99999</v>
       </c>
       <c r="K8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="1">
         <v>10</v>
@@ -1775,7 +1775,7 @@
         <v>99999</v>
       </c>
       <c r="K12" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" s="1">
         <v>30</v>
@@ -1816,7 +1816,7 @@
         <v>99999</v>
       </c>
       <c r="K13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="1">
         <v>30</v>
@@ -1857,7 +1857,7 @@
         <v>99999</v>
       </c>
       <c r="K14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="1">
         <v>20</v>
@@ -1898,7 +1898,7 @@
         <v>99999</v>
       </c>
       <c r="K15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" s="1">
         <v>30</v>
@@ -1980,10 +1980,10 @@
         <v>20</v>
       </c>
       <c r="K18" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L18" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M18" s="1">
         <v>1</v>
@@ -2021,10 +2021,10 @@
         <v>20</v>
       </c>
       <c r="K19" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L19" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M19" s="1">
         <v>1</v>
@@ -2062,10 +2062,10 @@
         <v>20</v>
       </c>
       <c r="K20" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L20" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M20" s="1">
         <v>1</v>
@@ -2431,7 +2431,7 @@
         <v>20</v>
       </c>
       <c r="K29" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <v>100</v>
@@ -2472,7 +2472,7 @@
         <v>20</v>
       </c>
       <c r="K30" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" s="3">
         <v>100</v>
@@ -2513,7 +2513,7 @@
         <v>20</v>
       </c>
       <c r="K31" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" s="3">
         <v>100</v>
@@ -2554,7 +2554,7 @@
         <v>20</v>
       </c>
       <c r="K32" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <v>100</v>
@@ -2595,7 +2595,7 @@
         <v>20</v>
       </c>
       <c r="K33" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" s="3">
         <v>100</v>
@@ -2636,7 +2636,7 @@
         <v>20</v>
       </c>
       <c r="K34" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L34" s="3">
         <v>100</v>
@@ -2677,7 +2677,7 @@
         <v>20</v>
       </c>
       <c r="K35" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="3">
         <v>100</v>
@@ -2718,7 +2718,7 @@
         <v>20</v>
       </c>
       <c r="K36" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="3">
         <v>100</v>
@@ -2759,7 +2759,7 @@
         <v>20</v>
       </c>
       <c r="K37" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" s="3">
         <v>100</v>
@@ -2806,10 +2806,10 @@
         <v>50</v>
       </c>
       <c r="K39" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L39" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M39" s="1">
         <v>1</v>
@@ -2847,10 +2847,10 @@
         <v>50</v>
       </c>
       <c r="K40" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L40" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M40" s="1">
         <v>1</v>
@@ -2888,10 +2888,10 @@
         <v>50</v>
       </c>
       <c r="K41" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L41" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M41" s="1">
         <v>1</v>
@@ -3257,7 +3257,7 @@
         <v>50</v>
       </c>
       <c r="K50" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L50" s="3">
         <v>100</v>
@@ -3298,7 +3298,7 @@
         <v>50</v>
       </c>
       <c r="K51" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" s="3">
         <v>100</v>
@@ -3339,7 +3339,7 @@
         <v>50</v>
       </c>
       <c r="K52" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
@@ -3380,7 +3380,7 @@
         <v>50</v>
       </c>
       <c r="K53" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L53" s="3">
         <v>100</v>
@@ -3421,7 +3421,7 @@
         <v>50</v>
       </c>
       <c r="K54" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L54" s="3">
         <v>100</v>
@@ -3462,7 +3462,7 @@
         <v>50</v>
       </c>
       <c r="K55" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L55" s="3">
         <v>100</v>
@@ -3503,7 +3503,7 @@
         <v>50</v>
       </c>
       <c r="K56" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L56" s="3">
         <v>100</v>
@@ -3544,7 +3544,7 @@
         <v>50</v>
       </c>
       <c r="K57" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
@@ -3585,7 +3585,7 @@
         <v>50</v>
       </c>
       <c r="K58" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L58" s="3">
         <v>100</v>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -1523,7 +1523,7 @@
         <v>19</v>
       </c>
       <c r="I6" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J6" s="1">
         <v>99999</v>
@@ -1532,7 +1532,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M6" s="1">
         <v>3</v>
@@ -1564,7 +1564,7 @@
         <v>21</v>
       </c>
       <c r="I7" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J7" s="1">
         <v>99999</v>
@@ -1573,7 +1573,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M7" s="1">
         <v>3</v>
@@ -1605,7 +1605,7 @@
         <v>22</v>
       </c>
       <c r="I8" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J8" s="1">
         <v>99999</v>
@@ -1614,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M8" s="1">
         <v>3</v>
@@ -1646,7 +1646,7 @@
         <v>24</v>
       </c>
       <c r="I9" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J9" s="1">
         <v>99999</v>
@@ -1655,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M9" s="1">
         <v>3</v>
@@ -1687,7 +1687,7 @@
         <v>9</v>
       </c>
       <c r="I10" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J10" s="1">
         <v>99999</v>
@@ -1696,7 +1696,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M10" s="1">
         <v>3</v>
@@ -1728,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J11" s="1">
         <v>99999</v>
@@ -1737,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M11" s="1">
         <v>3</v>
@@ -1769,7 +1769,7 @@
         <v>5</v>
       </c>
       <c r="I12" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J12" s="1">
         <v>99999</v>
@@ -1778,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="M12" s="1">
         <v>2</v>
@@ -1810,7 +1810,7 @@
         <v>5</v>
       </c>
       <c r="I13" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J13" s="1">
         <v>99999</v>
@@ -1819,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="M13" s="1">
         <v>2</v>
@@ -1851,7 +1851,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J14" s="1">
         <v>99999</v>
@@ -1860,7 +1860,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M14" s="1">
         <v>2</v>
@@ -1892,7 +1892,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J15" s="1">
         <v>99999</v>
@@ -1901,7 +1901,7 @@
         <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="M15" s="1">
         <v>2</v>
@@ -1933,7 +1933,7 @@
         <v>7</v>
       </c>
       <c r="I16" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J16" s="1">
         <v>99999</v>
@@ -1942,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M16" s="1">
         <v>2</v>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -3776,7 +3776,7 @@
         <v>30</v>
       </c>
       <c r="I6" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J6" s="1">
         <v>99999</v>
@@ -3817,7 +3817,7 @@
         <v>30</v>
       </c>
       <c r="I7" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J7" s="1">
         <v>99999</v>
@@ -3858,7 +3858,7 @@
         <v>30</v>
       </c>
       <c r="I8" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J8" s="1">
         <v>99999</v>
@@ -3899,7 +3899,7 @@
         <v>30</v>
       </c>
       <c r="I9" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J9" s="1">
         <v>99999</v>
@@ -3940,7 +3940,7 @@
         <v>30</v>
       </c>
       <c r="I10" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J10" s="1">
         <v>99999</v>
@@ -3981,7 +3981,7 @@
         <v>30</v>
       </c>
       <c r="I11" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J11" s="1">
         <v>99999</v>
@@ -4022,7 +4022,7 @@
         <v>30</v>
       </c>
       <c r="I12" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J12" s="1">
         <v>99999</v>
@@ -4063,7 +4063,7 @@
         <v>30</v>
       </c>
       <c r="I13" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J13" s="1">
         <v>99999</v>
@@ -4104,7 +4104,7 @@
         <v>30</v>
       </c>
       <c r="I14" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J14" s="1">
         <v>99999</v>
@@ -4145,7 +4145,7 @@
         <v>30</v>
       </c>
       <c r="I15" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J15" s="1">
         <v>99999</v>
@@ -4186,7 +4186,7 @@
         <v>30</v>
       </c>
       <c r="I16" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J16" s="1">
         <v>99999</v>
@@ -4227,7 +4227,7 @@
         <v>30</v>
       </c>
       <c r="I17" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J17" s="1">
         <v>99999</v>
@@ -4268,7 +4268,7 @@
         <v>30</v>
       </c>
       <c r="I18" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J18" s="1">
         <v>99999</v>
@@ -4309,7 +4309,7 @@
         <v>30</v>
       </c>
       <c r="I19" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J19" s="1">
         <v>99999</v>
@@ -4350,7 +4350,7 @@
         <v>30</v>
       </c>
       <c r="I20" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J20" s="1">
         <v>99999</v>
@@ -4391,7 +4391,7 @@
         <v>30</v>
       </c>
       <c r="I21" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J21" s="1">
         <v>99999</v>
@@ -4432,7 +4432,7 @@
         <v>30</v>
       </c>
       <c r="I22" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J22" s="1">
         <v>99999</v>
@@ -4473,7 +4473,7 @@
         <v>30</v>
       </c>
       <c r="I23" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J23" s="1">
         <v>99999</v>
@@ -4514,7 +4514,7 @@
         <v>30</v>
       </c>
       <c r="I24" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J24" s="1">
         <v>99999</v>
@@ -4555,7 +4555,7 @@
         <v>30</v>
       </c>
       <c r="I25" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J25" s="1">
         <v>99999</v>
@@ -4596,7 +4596,7 @@
         <v>30</v>
       </c>
       <c r="I26" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J26" s="1">
         <v>99999</v>
@@ -4637,7 +4637,7 @@
         <v>30</v>
       </c>
       <c r="I27" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J27" s="1">
         <v>99999</v>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -2109,7 +2114,7 @@
         <v>100</v>
       </c>
       <c r="M21" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21" s="1">
         <v>0</v>
@@ -2150,7 +2155,7 @@
         <v>100</v>
       </c>
       <c r="M22" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N22" s="1">
         <v>0</v>
@@ -2191,7 +2196,7 @@
         <v>100</v>
       </c>
       <c r="M23" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N23" s="1">
         <v>0</v>
@@ -2232,7 +2237,7 @@
         <v>100</v>
       </c>
       <c r="M24" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N24" s="1">
         <v>0</v>
@@ -2935,7 +2940,7 @@
         <v>100</v>
       </c>
       <c r="M42" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" s="1">
         <v>0</v>
@@ -2976,7 +2981,7 @@
         <v>100</v>
       </c>
       <c r="M43" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N43" s="1">
         <v>0</v>
@@ -3017,7 +3022,7 @@
         <v>100</v>
       </c>
       <c r="M44" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N44" s="1">
         <v>0</v>
@@ -3058,7 +3063,7 @@
         <v>100</v>
       </c>
       <c r="M45" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N45" s="1">
         <v>0</v>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -3045,7 +3045,7 @@
         <v>2</v>
       </c>
       <c r="G45" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H45" s="3">
         <v>5</v>
@@ -3083,10 +3083,10 @@
         <v>81</v>
       </c>
       <c r="F46" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>30</v>
@@ -3124,10 +3124,10 @@
         <v>82</v>
       </c>
       <c r="F47" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>30</v>
@@ -3165,10 +3165,10 @@
         <v>83</v>
       </c>
       <c r="F48" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>30</v>
@@ -3206,10 +3206,10 @@
         <v>84</v>
       </c>
       <c r="F49" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>30</v>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -173,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="73">
   <si>
     <t>#</t>
   </si>
@@ -1362,7 +1362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O58"/>
+  <dimension ref="C1:O79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2808,7 +2808,7 @@
         <v>21</v>
       </c>
       <c r="J39" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K39" s="1">
         <v>10</v>
@@ -2849,7 +2849,7 @@
         <v>21</v>
       </c>
       <c r="J40" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K40" s="1">
         <v>10</v>
@@ -2890,7 +2890,7 @@
         <v>21</v>
       </c>
       <c r="J41" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K41" s="1">
         <v>10</v>
@@ -2931,7 +2931,7 @@
         <v>21</v>
       </c>
       <c r="J42" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K42" s="1">
         <v>1</v>
@@ -2972,7 +2972,7 @@
         <v>21</v>
       </c>
       <c r="J43" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K43" s="1">
         <v>1</v>
@@ -3013,7 +3013,7 @@
         <v>21</v>
       </c>
       <c r="J44" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K44" s="1">
         <v>1</v>
@@ -3054,7 +3054,7 @@
         <v>21</v>
       </c>
       <c r="J45" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K45" s="1">
         <v>1</v>
@@ -3095,7 +3095,7 @@
         <v>21</v>
       </c>
       <c r="J46" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K46" s="1">
         <v>1</v>
@@ -3136,7 +3136,7 @@
         <v>21</v>
       </c>
       <c r="J47" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K47" s="1">
         <v>1</v>
@@ -3177,7 +3177,7 @@
         <v>21</v>
       </c>
       <c r="J48" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K48" s="1">
         <v>1</v>
@@ -3218,7 +3218,7 @@
         <v>21</v>
       </c>
       <c r="J49" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K49" s="1">
         <v>1</v>
@@ -3259,7 +3259,7 @@
         <v>21</v>
       </c>
       <c r="J50" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K50" s="1">
         <v>3</v>
@@ -3300,7 +3300,7 @@
         <v>21</v>
       </c>
       <c r="J51" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K51" s="1">
         <v>3</v>
@@ -3341,7 +3341,7 @@
         <v>21</v>
       </c>
       <c r="J52" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K52" s="1">
         <v>3</v>
@@ -3382,7 +3382,7 @@
         <v>21</v>
       </c>
       <c r="J53" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K53" s="1">
         <v>3</v>
@@ -3423,7 +3423,7 @@
         <v>21</v>
       </c>
       <c r="J54" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K54" s="1">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>21</v>
       </c>
       <c r="J55" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K55" s="1">
         <v>3</v>
@@ -3505,7 +3505,7 @@
         <v>21</v>
       </c>
       <c r="J56" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K56" s="1">
         <v>2</v>
@@ -3546,7 +3546,7 @@
         <v>21</v>
       </c>
       <c r="J57" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K57" s="1">
         <v>2</v>
@@ -3587,21 +3587,841 @@
         <v>21</v>
       </c>
       <c r="J58" s="1">
+        <v>60</v>
+      </c>
+      <c r="K58" s="1">
+        <v>2</v>
+      </c>
+      <c r="L58" s="3">
+        <v>100</v>
+      </c>
+      <c r="M58" s="1">
+        <v>1</v>
+      </c>
+      <c r="N58" s="1">
+        <v>3</v>
+      </c>
+      <c r="O58" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K58" s="1">
-        <v>2</v>
-      </c>
-      <c r="L58" s="3">
-        <v>100</v>
-      </c>
-      <c r="M58" s="1">
-        <v>1</v>
-      </c>
-      <c r="N58" s="1">
-        <v>3</v>
-      </c>
-      <c r="O58" s="1" t="s">
+    </row>
+    <row r="60" customHeight="1" spans="3:15">
+      <c r="C60" s="1">
+        <v>301</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1">
+        <v>500</v>
+      </c>
+      <c r="G60" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I60" s="1">
+        <v>61</v>
+      </c>
+      <c r="J60" s="1">
+        <v>110</v>
+      </c>
+      <c r="K60" s="1">
+        <v>10</v>
+      </c>
+      <c r="L60" s="3">
+        <v>300</v>
+      </c>
+      <c r="M60" s="1">
+        <v>1</v>
+      </c>
+      <c r="N60" s="1">
+        <v>0</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:15">
+      <c r="C61" s="1">
+        <v>302</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1</v>
+      </c>
+      <c r="E61" s="1">
+        <v>2</v>
+      </c>
+      <c r="F61" s="1">
+        <v>100</v>
+      </c>
+      <c r="G61" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I61" s="1">
+        <v>61</v>
+      </c>
+      <c r="J61" s="1">
+        <v>110</v>
+      </c>
+      <c r="K61" s="1">
+        <v>10</v>
+      </c>
+      <c r="L61" s="3">
+        <v>300</v>
+      </c>
+      <c r="M61" s="1">
+        <v>1</v>
+      </c>
+      <c r="N61" s="1">
+        <v>0</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:15">
+      <c r="C62" s="1">
+        <v>303</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1</v>
+      </c>
+      <c r="E62" s="1">
+        <v>3</v>
+      </c>
+      <c r="F62" s="1">
+        <v>100</v>
+      </c>
+      <c r="G62" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I62" s="1">
+        <v>61</v>
+      </c>
+      <c r="J62" s="1">
+        <v>110</v>
+      </c>
+      <c r="K62" s="1">
+        <v>10</v>
+      </c>
+      <c r="L62" s="3">
+        <v>300</v>
+      </c>
+      <c r="M62" s="1">
+        <v>1</v>
+      </c>
+      <c r="N62" s="1">
+        <v>0</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:15">
+      <c r="C63" s="1">
+        <v>304</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1</v>
+      </c>
+      <c r="E63" s="1">
+        <v>21</v>
+      </c>
+      <c r="F63" s="1">
+        <v>2</v>
+      </c>
+      <c r="G63" s="1">
+        <v>5</v>
+      </c>
+      <c r="H63" s="3">
+        <v>9</v>
+      </c>
+      <c r="I63" s="1">
+        <v>61</v>
+      </c>
+      <c r="J63" s="1">
+        <v>110</v>
+      </c>
+      <c r="K63" s="1">
+        <v>1</v>
+      </c>
+      <c r="L63" s="3">
+        <v>100</v>
+      </c>
+      <c r="M63" s="1">
+        <v>2</v>
+      </c>
+      <c r="N63" s="1">
+        <v>0</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:15">
+      <c r="C64" s="1">
+        <v>305</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1</v>
+      </c>
+      <c r="E64" s="1">
+        <v>22</v>
+      </c>
+      <c r="F64" s="1">
+        <v>10</v>
+      </c>
+      <c r="G64" s="1">
+        <v>40</v>
+      </c>
+      <c r="H64" s="3">
+        <v>10</v>
+      </c>
+      <c r="I64" s="1">
+        <v>61</v>
+      </c>
+      <c r="J64" s="1">
+        <v>110</v>
+      </c>
+      <c r="K64" s="1">
+        <v>1</v>
+      </c>
+      <c r="L64" s="3">
+        <v>100</v>
+      </c>
+      <c r="M64" s="1">
+        <v>2</v>
+      </c>
+      <c r="N64" s="1">
+        <v>0</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:15">
+      <c r="C65" s="1">
+        <v>306</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="E65" s="1">
+        <v>27</v>
+      </c>
+      <c r="F65" s="1">
+        <v>2</v>
+      </c>
+      <c r="G65" s="1">
+        <v>10</v>
+      </c>
+      <c r="H65" s="3">
+        <v>7</v>
+      </c>
+      <c r="I65" s="1">
+        <v>61</v>
+      </c>
+      <c r="J65" s="1">
+        <v>110</v>
+      </c>
+      <c r="K65" s="1">
+        <v>1</v>
+      </c>
+      <c r="L65" s="3">
+        <v>100</v>
+      </c>
+      <c r="M65" s="1">
+        <v>2</v>
+      </c>
+      <c r="N65" s="1">
+        <v>0</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:15">
+      <c r="C66" s="1">
+        <v>307</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+      <c r="E66" s="1">
+        <v>28</v>
+      </c>
+      <c r="F66" s="1">
+        <v>2</v>
+      </c>
+      <c r="G66" s="1">
+        <v>6</v>
+      </c>
+      <c r="H66" s="3">
+        <v>5</v>
+      </c>
+      <c r="I66" s="1">
+        <v>61</v>
+      </c>
+      <c r="J66" s="1">
+        <v>110</v>
+      </c>
+      <c r="K66" s="1">
+        <v>1</v>
+      </c>
+      <c r="L66" s="3">
+        <v>100</v>
+      </c>
+      <c r="M66" s="1">
+        <v>2</v>
+      </c>
+      <c r="N66" s="1">
+        <v>0</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:15">
+      <c r="C67" s="1">
+        <v>308</v>
+      </c>
+      <c r="D67" s="1">
+        <v>1</v>
+      </c>
+      <c r="E67" s="1">
+        <v>81</v>
+      </c>
+      <c r="F67" s="1">
+        <v>1</v>
+      </c>
+      <c r="G67" s="1">
+        <v>4</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I67" s="1">
+        <v>61</v>
+      </c>
+      <c r="J67" s="1">
+        <v>110</v>
+      </c>
+      <c r="K67" s="1">
+        <v>1</v>
+      </c>
+      <c r="L67" s="3">
+        <v>100</v>
+      </c>
+      <c r="M67" s="1">
+        <v>2</v>
+      </c>
+      <c r="N67" s="1">
+        <v>0</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:15">
+      <c r="C68" s="1">
+        <v>309</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" s="1">
+        <v>82</v>
+      </c>
+      <c r="F68" s="1">
+        <v>1</v>
+      </c>
+      <c r="G68" s="1">
+        <v>4</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I68" s="1">
+        <v>61</v>
+      </c>
+      <c r="J68" s="1">
+        <v>110</v>
+      </c>
+      <c r="K68" s="1">
+        <v>1</v>
+      </c>
+      <c r="L68" s="3">
+        <v>100</v>
+      </c>
+      <c r="M68" s="1">
+        <v>2</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:15">
+      <c r="C69" s="1">
+        <v>310</v>
+      </c>
+      <c r="D69" s="1">
+        <v>1</v>
+      </c>
+      <c r="E69" s="1">
+        <v>83</v>
+      </c>
+      <c r="F69" s="1">
+        <v>1</v>
+      </c>
+      <c r="G69" s="1">
+        <v>4</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I69" s="1">
+        <v>61</v>
+      </c>
+      <c r="J69" s="1">
+        <v>110</v>
+      </c>
+      <c r="K69" s="1">
+        <v>1</v>
+      </c>
+      <c r="L69" s="3">
+        <v>100</v>
+      </c>
+      <c r="M69" s="1">
+        <v>2</v>
+      </c>
+      <c r="N69" s="1">
+        <v>0</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:15">
+      <c r="C70" s="1">
+        <v>311</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1</v>
+      </c>
+      <c r="E70" s="1">
+        <v>84</v>
+      </c>
+      <c r="F70" s="1">
+        <v>1</v>
+      </c>
+      <c r="G70" s="1">
+        <v>4</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I70" s="1">
+        <v>61</v>
+      </c>
+      <c r="J70" s="1">
+        <v>110</v>
+      </c>
+      <c r="K70" s="1">
+        <v>1</v>
+      </c>
+      <c r="L70" s="3">
+        <v>100</v>
+      </c>
+      <c r="M70" s="1">
+        <v>2</v>
+      </c>
+      <c r="N70" s="1">
+        <v>0</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:15">
+      <c r="C71" s="1">
+        <v>312</v>
+      </c>
+      <c r="D71" s="1">
+        <v>1</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1001</v>
+      </c>
+      <c r="F71" s="1">
+        <v>10</v>
+      </c>
+      <c r="G71" s="1">
+        <v>40</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I71" s="1">
+        <v>61</v>
+      </c>
+      <c r="J71" s="1">
+        <v>110</v>
+      </c>
+      <c r="K71" s="1">
+        <v>3</v>
+      </c>
+      <c r="L71" s="3">
+        <v>100</v>
+      </c>
+      <c r="M71" s="1">
+        <v>1</v>
+      </c>
+      <c r="N71" s="1">
+        <v>0</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:15">
+      <c r="C72" s="1">
+        <v>313</v>
+      </c>
+      <c r="D72" s="1">
+        <v>1</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1002</v>
+      </c>
+      <c r="F72" s="1">
+        <v>5</v>
+      </c>
+      <c r="G72" s="1">
+        <v>20</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I72" s="1">
+        <v>61</v>
+      </c>
+      <c r="J72" s="1">
+        <v>110</v>
+      </c>
+      <c r="K72" s="1">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3">
+        <v>100</v>
+      </c>
+      <c r="M72" s="1">
+        <v>1</v>
+      </c>
+      <c r="N72" s="1">
+        <v>0</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:15">
+      <c r="C73" s="1">
+        <v>314</v>
+      </c>
+      <c r="D73" s="1">
+        <v>1</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1003</v>
+      </c>
+      <c r="F73" s="1">
+        <v>2</v>
+      </c>
+      <c r="G73" s="1">
+        <v>10</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I73" s="1">
+        <v>61</v>
+      </c>
+      <c r="J73" s="1">
+        <v>110</v>
+      </c>
+      <c r="K73" s="1">
+        <v>3</v>
+      </c>
+      <c r="L73" s="3">
+        <v>100</v>
+      </c>
+      <c r="M73" s="1">
+        <v>1</v>
+      </c>
+      <c r="N73" s="1">
+        <v>0</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:15">
+      <c r="C74" s="1">
+        <v>315</v>
+      </c>
+      <c r="D74" s="1">
+        <v>1</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1004</v>
+      </c>
+      <c r="F74" s="1">
+        <v>3</v>
+      </c>
+      <c r="G74" s="1">
+        <v>15</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I74" s="1">
+        <v>61</v>
+      </c>
+      <c r="J74" s="1">
+        <v>110</v>
+      </c>
+      <c r="K74" s="1">
+        <v>3</v>
+      </c>
+      <c r="L74" s="3">
+        <v>100</v>
+      </c>
+      <c r="M74" s="1">
+        <v>1</v>
+      </c>
+      <c r="N74" s="1">
+        <v>1</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:15">
+      <c r="C75" s="1">
+        <v>316</v>
+      </c>
+      <c r="D75" s="1">
+        <v>1</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1005</v>
+      </c>
+      <c r="F75" s="1">
+        <v>3</v>
+      </c>
+      <c r="G75" s="1">
+        <v>15</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I75" s="1">
+        <v>61</v>
+      </c>
+      <c r="J75" s="1">
+        <v>110</v>
+      </c>
+      <c r="K75" s="1">
+        <v>3</v>
+      </c>
+      <c r="L75" s="3">
+        <v>100</v>
+      </c>
+      <c r="M75" s="1">
+        <v>1</v>
+      </c>
+      <c r="N75" s="1">
+        <v>2</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:15">
+      <c r="C76" s="1">
+        <v>317</v>
+      </c>
+      <c r="D76" s="1">
+        <v>1</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1006</v>
+      </c>
+      <c r="F76" s="1">
+        <v>3</v>
+      </c>
+      <c r="G76" s="1">
+        <v>15</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I76" s="1">
+        <v>61</v>
+      </c>
+      <c r="J76" s="1">
+        <v>110</v>
+      </c>
+      <c r="K76" s="1">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3">
+        <v>100</v>
+      </c>
+      <c r="M76" s="1">
+        <v>1</v>
+      </c>
+      <c r="N76" s="1">
+        <v>3</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:15">
+      <c r="C77" s="1">
+        <v>318</v>
+      </c>
+      <c r="D77" s="1">
+        <v>1</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1007</v>
+      </c>
+      <c r="F77" s="1">
+        <v>3</v>
+      </c>
+      <c r="G77" s="1">
+        <v>15</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I77" s="1">
+        <v>61</v>
+      </c>
+      <c r="J77" s="1">
+        <v>110</v>
+      </c>
+      <c r="K77" s="1">
+        <v>2</v>
+      </c>
+      <c r="L77" s="3">
+        <v>100</v>
+      </c>
+      <c r="M77" s="1">
+        <v>1</v>
+      </c>
+      <c r="N77" s="1">
+        <v>1</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:15">
+      <c r="C78" s="1">
+        <v>319</v>
+      </c>
+      <c r="D78" s="1">
+        <v>1</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1008</v>
+      </c>
+      <c r="F78" s="1">
+        <v>3</v>
+      </c>
+      <c r="G78" s="1">
+        <v>15</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I78" s="1">
+        <v>61</v>
+      </c>
+      <c r="J78" s="1">
+        <v>110</v>
+      </c>
+      <c r="K78" s="1">
+        <v>2</v>
+      </c>
+      <c r="L78" s="3">
+        <v>100</v>
+      </c>
+      <c r="M78" s="1">
+        <v>1</v>
+      </c>
+      <c r="N78" s="1">
+        <v>2</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:15">
+      <c r="C79" s="1">
+        <v>320</v>
+      </c>
+      <c r="D79" s="1">
+        <v>1</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1009</v>
+      </c>
+      <c r="F79" s="1">
+        <v>3</v>
+      </c>
+      <c r="G79" s="1">
+        <v>15</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I79" s="1">
+        <v>61</v>
+      </c>
+      <c r="J79" s="1">
+        <v>110</v>
+      </c>
+      <c r="K79" s="1">
+        <v>2</v>
+      </c>
+      <c r="L79" s="3">
+        <v>100</v>
+      </c>
+      <c r="M79" s="1">
+        <v>1</v>
+      </c>
+      <c r="N79" s="1">
+        <v>3</v>
+      </c>
+      <c r="O79" s="1" t="s">
         <v>50</v>
       </c>
     </row>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -1528,7 +1528,7 @@
         <v>19</v>
       </c>
       <c r="I6" s="1">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J6" s="1">
         <v>99999</v>
@@ -1569,7 +1569,7 @@
         <v>21</v>
       </c>
       <c r="I7" s="1">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J7" s="1">
         <v>99999</v>
@@ -1610,7 +1610,7 @@
         <v>22</v>
       </c>
       <c r="I8" s="1">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J8" s="1">
         <v>99999</v>
@@ -1651,7 +1651,7 @@
         <v>24</v>
       </c>
       <c r="I9" s="1">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J9" s="1">
         <v>99999</v>
@@ -1692,7 +1692,7 @@
         <v>9</v>
       </c>
       <c r="I10" s="1">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J10" s="1">
         <v>99999</v>
@@ -1733,7 +1733,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="1">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J11" s="1">
         <v>99999</v>
@@ -1774,7 +1774,7 @@
         <v>5</v>
       </c>
       <c r="I12" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J12" s="1">
         <v>99999</v>
@@ -1815,7 +1815,7 @@
         <v>5</v>
       </c>
       <c r="I13" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J13" s="1">
         <v>99999</v>
@@ -1856,7 +1856,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J14" s="1">
         <v>99999</v>
@@ -1897,7 +1897,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J15" s="1">
         <v>99999</v>
@@ -1938,7 +1938,7 @@
         <v>7</v>
       </c>
       <c r="I16" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J16" s="1">
         <v>99999</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K18" s="1">
         <v>10</v>
@@ -2023,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K19" s="1">
         <v>10</v>
@@ -2064,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K20" s="1">
         <v>10</v>
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K21" s="1">
         <v>1</v>
@@ -2146,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K22" s="1">
         <v>1</v>
@@ -2187,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K23" s="1">
         <v>1</v>
@@ -2228,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K24" s="1">
         <v>1</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K25" s="1">
         <v>1</v>
@@ -2310,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K26" s="1">
         <v>1</v>
@@ -2351,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K27" s="1">
         <v>1</v>
@@ -2392,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K28" s="1">
         <v>1</v>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K29" s="1">
         <v>3</v>
@@ -2474,7 +2474,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K30" s="1">
         <v>3</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K31" s="1">
         <v>3</v>
@@ -2556,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K32" s="1">
         <v>3</v>
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K33" s="1">
         <v>3</v>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K34" s="1">
         <v>3</v>
@@ -2679,7 +2679,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K35" s="1">
         <v>2</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K36" s="1">
         <v>2</v>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K37" s="1">
         <v>2</v>
@@ -2805,10 +2805,10 @@
         <v>30</v>
       </c>
       <c r="I39" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J39" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K39" s="1">
         <v>10</v>
@@ -2846,10 +2846,10 @@
         <v>30</v>
       </c>
       <c r="I40" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J40" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K40" s="1">
         <v>10</v>
@@ -2887,10 +2887,10 @@
         <v>30</v>
       </c>
       <c r="I41" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J41" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K41" s="1">
         <v>10</v>
@@ -2928,10 +2928,10 @@
         <v>9</v>
       </c>
       <c r="I42" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J42" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K42" s="1">
         <v>1</v>
@@ -2969,10 +2969,10 @@
         <v>10</v>
       </c>
       <c r="I43" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J43" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K43" s="1">
         <v>1</v>
@@ -3010,10 +3010,10 @@
         <v>7</v>
       </c>
       <c r="I44" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J44" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K44" s="1">
         <v>1</v>
@@ -3051,10 +3051,10 @@
         <v>5</v>
       </c>
       <c r="I45" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J45" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K45" s="1">
         <v>1</v>
@@ -3092,10 +3092,10 @@
         <v>30</v>
       </c>
       <c r="I46" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J46" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K46" s="1">
         <v>1</v>
@@ -3133,10 +3133,10 @@
         <v>30</v>
       </c>
       <c r="I47" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J47" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K47" s="1">
         <v>1</v>
@@ -3174,10 +3174,10 @@
         <v>30</v>
       </c>
       <c r="I48" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J48" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K48" s="1">
         <v>1</v>
@@ -3215,10 +3215,10 @@
         <v>30</v>
       </c>
       <c r="I49" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J49" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K49" s="1">
         <v>1</v>
@@ -3256,10 +3256,10 @@
         <v>30</v>
       </c>
       <c r="I50" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J50" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K50" s="1">
         <v>3</v>
@@ -3297,10 +3297,10 @@
         <v>30</v>
       </c>
       <c r="I51" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J51" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K51" s="1">
         <v>3</v>
@@ -3338,10 +3338,10 @@
         <v>30</v>
       </c>
       <c r="I52" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J52" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K52" s="1">
         <v>3</v>
@@ -3379,10 +3379,10 @@
         <v>30</v>
       </c>
       <c r="I53" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J53" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K53" s="1">
         <v>3</v>
@@ -3420,10 +3420,10 @@
         <v>30</v>
       </c>
       <c r="I54" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J54" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K54" s="1">
         <v>3</v>
@@ -3461,10 +3461,10 @@
         <v>30</v>
       </c>
       <c r="I55" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J55" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K55" s="1">
         <v>3</v>
@@ -3502,10 +3502,10 @@
         <v>30</v>
       </c>
       <c r="I56" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J56" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K56" s="1">
         <v>2</v>
@@ -3543,10 +3543,10 @@
         <v>30</v>
       </c>
       <c r="I57" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J57" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K57" s="1">
         <v>2</v>
@@ -3584,10 +3584,10 @@
         <v>30</v>
       </c>
       <c r="I58" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J58" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K58" s="1">
         <v>2</v>
@@ -3625,10 +3625,10 @@
         <v>30</v>
       </c>
       <c r="I60" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J60" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K60" s="1">
         <v>10</v>
@@ -3666,10 +3666,10 @@
         <v>30</v>
       </c>
       <c r="I61" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J61" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K61" s="1">
         <v>10</v>
@@ -3707,10 +3707,10 @@
         <v>30</v>
       </c>
       <c r="I62" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J62" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K62" s="1">
         <v>10</v>
@@ -3748,10 +3748,10 @@
         <v>9</v>
       </c>
       <c r="I63" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J63" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K63" s="1">
         <v>1</v>
@@ -3789,10 +3789,10 @@
         <v>10</v>
       </c>
       <c r="I64" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J64" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K64" s="1">
         <v>1</v>
@@ -3830,10 +3830,10 @@
         <v>7</v>
       </c>
       <c r="I65" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J65" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K65" s="1">
         <v>1</v>
@@ -3871,10 +3871,10 @@
         <v>5</v>
       </c>
       <c r="I66" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J66" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K66" s="1">
         <v>1</v>
@@ -3912,10 +3912,10 @@
         <v>30</v>
       </c>
       <c r="I67" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J67" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K67" s="1">
         <v>1</v>
@@ -3953,10 +3953,10 @@
         <v>30</v>
       </c>
       <c r="I68" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J68" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K68" s="1">
         <v>1</v>
@@ -3994,10 +3994,10 @@
         <v>30</v>
       </c>
       <c r="I69" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J69" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K69" s="1">
         <v>1</v>
@@ -4035,10 +4035,10 @@
         <v>30</v>
       </c>
       <c r="I70" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J70" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K70" s="1">
         <v>1</v>
@@ -4076,10 +4076,10 @@
         <v>30</v>
       </c>
       <c r="I71" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J71" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K71" s="1">
         <v>3</v>
@@ -4117,10 +4117,10 @@
         <v>30</v>
       </c>
       <c r="I72" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J72" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K72" s="1">
         <v>3</v>
@@ -4158,10 +4158,10 @@
         <v>30</v>
       </c>
       <c r="I73" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J73" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K73" s="1">
         <v>3</v>
@@ -4199,10 +4199,10 @@
         <v>30</v>
       </c>
       <c r="I74" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J74" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K74" s="1">
         <v>3</v>
@@ -4240,10 +4240,10 @@
         <v>30</v>
       </c>
       <c r="I75" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J75" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K75" s="1">
         <v>3</v>
@@ -4281,10 +4281,10 @@
         <v>30</v>
       </c>
       <c r="I76" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J76" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K76" s="1">
         <v>3</v>
@@ -4322,10 +4322,10 @@
         <v>30</v>
       </c>
       <c r="I77" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J77" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K77" s="1">
         <v>2</v>
@@ -4363,10 +4363,10 @@
         <v>30</v>
       </c>
       <c r="I78" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J78" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K78" s="1">
         <v>2</v>
@@ -4404,10 +4404,10 @@
         <v>30</v>
       </c>
       <c r="I79" s="1">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J79" s="1">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K79" s="1">
         <v>2</v>
@@ -4601,7 +4601,7 @@
         <v>30</v>
       </c>
       <c r="I6" s="1">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="J6" s="1">
         <v>99999</v>
@@ -4642,7 +4642,7 @@
         <v>30</v>
       </c>
       <c r="I7" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J7" s="1">
         <v>99999</v>
@@ -4683,7 +4683,7 @@
         <v>30</v>
       </c>
       <c r="I8" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J8" s="1">
         <v>99999</v>
@@ -4724,7 +4724,7 @@
         <v>30</v>
       </c>
       <c r="I9" s="1">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J9" s="1">
         <v>99999</v>
@@ -4765,7 +4765,7 @@
         <v>30</v>
       </c>
       <c r="I10" s="1">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J10" s="1">
         <v>99999</v>
@@ -4806,7 +4806,7 @@
         <v>30</v>
       </c>
       <c r="I11" s="1">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="J11" s="1">
         <v>99999</v>
@@ -4847,7 +4847,7 @@
         <v>30</v>
       </c>
       <c r="I12" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="J12" s="1">
         <v>99999</v>
@@ -4888,7 +4888,7 @@
         <v>30</v>
       </c>
       <c r="I13" s="1">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="J13" s="1">
         <v>99999</v>
@@ -4929,7 +4929,7 @@
         <v>30</v>
       </c>
       <c r="I14" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J14" s="1">
         <v>99999</v>
@@ -4970,7 +4970,7 @@
         <v>30</v>
       </c>
       <c r="I15" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J15" s="1">
         <v>99999</v>
@@ -5011,7 +5011,7 @@
         <v>30</v>
       </c>
       <c r="I16" s="1">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J16" s="1">
         <v>99999</v>
@@ -5052,7 +5052,7 @@
         <v>30</v>
       </c>
       <c r="I17" s="1">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J17" s="1">
         <v>99999</v>
@@ -5093,7 +5093,7 @@
         <v>30</v>
       </c>
       <c r="I18" s="1">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="J18" s="1">
         <v>99999</v>
@@ -5134,7 +5134,7 @@
         <v>30</v>
       </c>
       <c r="I19" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="J19" s="1">
         <v>99999</v>
@@ -5175,7 +5175,7 @@
         <v>30</v>
       </c>
       <c r="I20" s="1">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="J20" s="1">
         <v>99999</v>
@@ -5216,7 +5216,7 @@
         <v>30</v>
       </c>
       <c r="I21" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J21" s="1">
         <v>99999</v>
@@ -5257,7 +5257,7 @@
         <v>30</v>
       </c>
       <c r="I22" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J22" s="1">
         <v>99999</v>
@@ -5298,7 +5298,7 @@
         <v>30</v>
       </c>
       <c r="I23" s="1">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J23" s="1">
         <v>99999</v>
@@ -5339,7 +5339,7 @@
         <v>30</v>
       </c>
       <c r="I24" s="1">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J24" s="1">
         <v>99999</v>
@@ -5380,7 +5380,7 @@
         <v>30</v>
       </c>
       <c r="I25" s="1">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="J25" s="1">
         <v>99999</v>
@@ -5421,7 +5421,7 @@
         <v>30</v>
       </c>
       <c r="I26" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="J26" s="1">
         <v>99999</v>
@@ -5462,7 +5462,7 @@
         <v>30</v>
       </c>
       <c r="I27" s="1">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="J27" s="1">
         <v>99999</v>
